--- a/public/post/drafts/season-prediction/men_breakthrough-predictions-2025-final.xlsx
+++ b/public/post/drafts/season-prediction/men_breakthrough-predictions-2025-final.xlsx
@@ -40,19 +40,31 @@
     <t xml:space="preserve">Model_Confidence</t>
   </si>
   <si>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
+  </si>
+  <si>
     <t xml:space="preserve">Age</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp</t>
+    <t xml:space="preserve">Prev_Sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_C</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_F</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_C</t>
+    <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
   </si>
   <si>
     <t xml:space="preserve">William Poromaa</t>
@@ -61,28 +73,22 @@
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">Very Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ben Ogden</t>
   </si>
   <si>
     <t xml:space="preserve">USA</t>
   </si>
   <si>
+    <t xml:space="preserve">Even Northug</t>
+  </si>
+  <si>
     <t xml:space="preserve">Simen Hegstad Krüger</t>
   </si>
   <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
     <t xml:space="preserve">Didrik Tønseth</t>
   </si>
   <si>
-    <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
+    <t xml:space="preserve">Edvin Anger</t>
   </si>
   <si>
     <t xml:space="preserve">Friedrich Moch</t>
@@ -91,7 +97,10 @@
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t xml:space="preserve">Edvin Anger</t>
+    <t xml:space="preserve">Antoine Cyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
   </si>
   <si>
     <t xml:space="preserve">Michal Novak</t>
@@ -100,13 +109,10 @@
     <t xml:space="preserve">Czechia</t>
   </si>
   <si>
-    <t xml:space="preserve">Even Northug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antoine Cyr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
+    <t xml:space="preserve">Valerio Grond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
   </si>
   <si>
     <t xml:space="preserve">Richard Jouve</t>
@@ -118,169 +124,193 @@
     <t xml:space="preserve">Hugo Lapalus</t>
   </si>
   <si>
-    <t xml:space="preserve">Valerio Grond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
+    <t xml:space="preserve">Jules Chappaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu Hyvärinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Chanavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gus Schumacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Vuorinen</t>
   </si>
   <si>
     <t xml:space="preserve">Jens Burman</t>
   </si>
   <si>
-    <t xml:space="preserve">Gus Schumacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Chappaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Vuorinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu Hyvärinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Chanavat</t>
-  </si>
-  <si>
     <t xml:space="preserve">James Clinton Schoonmaker</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Solås Taugbøl</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mika Vermeulen</t>
   </si>
   <si>
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
+    <t xml:space="preserve">Joni Mäki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattis Stenshagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niilo Moilanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Schely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Thomas Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ristomatti Hakola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beda Klee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Häggström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davide Graz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyril Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaud Jay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Lindholm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andrew Musgrave</t>
   </si>
   <si>
     <t xml:space="preserve">Great Britain</t>
   </si>
   <si>
-    <t xml:space="preserve">Niilo Moilanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joni Mäki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beda Klee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo Schely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattis Stenshagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Solås Taugbøl</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oskar Svensson</t>
   </si>
   <si>
-    <t xml:space="preserve">Ristomatti Hakola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Lapierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyril Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davide Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Thomas Jenssen</t>
+    <t xml:space="preserve">Markus Vuorela</t>
   </si>
   <si>
     <t xml:space="preserve">Zanden McMullen</t>
   </si>
   <si>
-    <t xml:space="preserve">Renaud Jay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markus Vuorela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Lindholm</t>
-  </si>
-  <si>
     <t xml:space="preserve">Leo Johansson</t>
   </si>
   <si>
+    <t xml:space="preserve">Janik Riebli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henrik Dønnestad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matz William Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansgar Evensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
     <t xml:space="preserve">Janosch Brugger</t>
   </si>
   <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janik Riebli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remi Bourdin</t>
   </si>
   <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naoto Baba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludek Seller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Moser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anian Sossau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xavier McKeever</t>
   </si>
   <si>
-    <t xml:space="preserve">Matz William Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
+    <t xml:space="preserve">Lauri Lepistö</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Dapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustaf Berglund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
   </si>
   <si>
     <t xml:space="preserve">Jonas Baumann</t>
   </si>
   <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naoto Baba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ansgar Evensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henrik Dønnestad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anian Sossau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Lepistö</t>
-  </si>
-  <si>
     <t xml:space="preserve">Florian Notz</t>
   </si>
   <si>
-    <t xml:space="preserve">Benjamin Moser</t>
+    <t xml:space="preserve">Johnny Hagenbuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Hirose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sasha Masson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Hellweger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Patterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Föttinger</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas Hjalmar Westgård</t>
@@ -289,40 +319,37 @@
     <t xml:space="preserve">Ireland</t>
   </si>
   <si>
+    <t xml:space="preserve">Paolo Ventura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Giandomenico Salvadori</t>
   </si>
   <si>
-    <t xml:space="preserve">Simone Dapra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludek Seller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustaf Berglund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sasha Masson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Ketterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryo Hirose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Patterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johnny Hagenbuch</t>
+    <t xml:space="preserve">James Clugnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bögl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre Grall-Johnson</t>
   </si>
   <si>
     <t xml:space="preserve">Dietmar Nöckler</t>
   </si>
   <si>
-    <t xml:space="preserve">Paolo Ventura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bögl</t>
+    <t xml:space="preserve">Luke Jager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman Schaad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Earnhart</t>
   </si>
   <si>
     <t xml:space="preserve">Miha Simenc</t>
@@ -334,25 +361,7 @@
     <t xml:space="preserve">Andrew Young</t>
   </si>
   <si>
-    <t xml:space="preserve">James Clugnet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Föttinger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Himma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Jager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Hellweger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Earnhart</t>
+    <t xml:space="preserve">Kevin Bolger</t>
   </si>
   <si>
     <t xml:space="preserve">Dominik Bury</t>
@@ -361,112 +370,103 @@
     <t xml:space="preserve">Poland</t>
   </si>
   <si>
-    <t xml:space="preserve">Pierre Grall-Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin Bolger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roman Schaad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adam Fellner</t>
   </si>
   <si>
+    <t xml:space="preserve">Candide Pralong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Wolter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anze Gros</t>
   </si>
   <si>
+    <t xml:space="preserve">Leo Grandbois</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vili Crv</t>
   </si>
   <si>
-    <t xml:space="preserve">Leo Grandbois</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nikita Gridin</t>
   </si>
   <si>
     <t xml:space="preserve">Kazakhstan</t>
   </si>
   <si>
-    <t xml:space="preserve">Peter Wolter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candide Pralong</t>
+    <t xml:space="preserve">Erwan Käser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fedor Karpov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamil Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konstantin Bortsov</t>
   </si>
   <si>
     <t xml:space="preserve">Maciej Starega</t>
   </si>
   <si>
-    <t xml:space="preserve">Kamil Bury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erwan Käser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Johannes Alev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fedor Karpov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konstantin Bortsov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seve De Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Australia</t>
   </si>
   <si>
+    <t xml:space="preserve">Imanol Rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simeon Deyanov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Olzhas Klimin</t>
   </si>
   <si>
-    <t xml:space="preserve">Imanol Rojo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simeon Deyanov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
+    <t xml:space="preserve">Julien Locke</t>
   </si>
   <si>
     <t xml:space="preserve">Vladislav Kovalyov</t>
   </si>
   <si>
-    <t xml:space="preserve">Julien Locke</t>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points_mean</t>
   </si>
   <si>
     <t xml:space="preserve">Age_mean</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exp_mean</t>
+    <t xml:space="preserve">Prev_Sprint_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prev_C_mean</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_F_mean</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_C_mean</t>
-  </si>
-  <si>
     <t xml:space="preserve">Predictors_Used</t>
   </si>
   <si>
     <t xml:space="preserve">Model_ROC</t>
   </si>
   <si>
-    <t xml:space="preserve">Age, Prev_Pct_of_Max_Points, Exp, Prev_F, Prev_C</t>
+    <t xml:space="preserve">Prev_Pct_of_Max_Points, Age, Prev_Sprint, Prev_C, Prev_F</t>
   </si>
 </sst>
 </file>
@@ -844,16 +844,16 @@
         <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>0.314461538461538</v>
+        <v>0.458769230769231</v>
       </c>
       <c r="D2" t="n">
-        <v>0.314461538461538</v>
+        <v>0.458769230769231</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0551465950060405</v>
+        <v>0.0610950460892711</v>
       </c>
       <c r="F2" t="n">
-        <v>0.185538461538462</v>
+        <v>0.0412307692307692</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -862,19 +862,19 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>23.2306639288159</v>
+        <v>0.272982456140351</v>
       </c>
       <c r="J2" t="n">
-        <v>0.322456140350877</v>
+        <v>31.958932238193</v>
       </c>
       <c r="K2" t="n">
-        <v>81</v>
+        <v>1379.07199098257</v>
       </c>
       <c r="L2" t="n">
-        <v>1524.82361908068</v>
+        <v>1706.83124302639</v>
       </c>
       <c r="M2" t="n">
-        <v>1541.94472735067</v>
+        <v>1581.73500270191</v>
       </c>
     </row>
     <row r="3">
@@ -885,16 +885,16 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>0.241846153846154</v>
+        <v>0.314461538461538</v>
       </c>
       <c r="D3" t="n">
-        <v>0.365084745762712</v>
+        <v>0.314461538461538</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0466148508150617</v>
+        <v>0.049768435335312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.258153846153846</v>
+        <v>0.185538461538462</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -903,19 +903,19 @@
         <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>23.9917864476386</v>
+        <v>0.322456140350877</v>
       </c>
       <c r="J3" t="n">
-        <v>0.377894736842105</v>
+        <v>23.2306639288159</v>
       </c>
       <c r="K3" t="n">
-        <v>74</v>
+        <v>1317.52297936676</v>
       </c>
       <c r="L3" t="n">
-        <v>1469.7451665932</v>
+        <v>1541.94472735067</v>
       </c>
       <c r="M3" t="n">
-        <v>1536.84453870404</v>
+        <v>1524.82361908068</v>
       </c>
     </row>
     <row r="4">
@@ -926,16 +926,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.313230769230769</v>
+        <v>0.241846153846154</v>
       </c>
       <c r="D4" t="n">
-        <v>0.498095238095238</v>
+        <v>0.365084745762712</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0443275651012195</v>
+        <v>0.049080761531926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.186769230769231</v>
+        <v>0.258153846153846</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -944,19 +944,19 @@
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>30.9924709103354</v>
+        <v>0.377894736842105</v>
       </c>
       <c r="J4" t="n">
-        <v>0.459649122807018</v>
+        <v>23.9917864476386</v>
       </c>
       <c r="K4" t="n">
-        <v>160</v>
+        <v>1657.30372953512</v>
       </c>
       <c r="L4" t="n">
-        <v>1660.82001426084</v>
+        <v>1536.84453870404</v>
       </c>
       <c r="M4" t="n">
-        <v>1557.96605530036</v>
+        <v>1469.7451665932</v>
       </c>
     </row>
     <row r="5">
@@ -964,19 +964,19 @@
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>0.268615384615385</v>
+        <v>0.264307692307692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.443606557377049</v>
+        <v>0.292881355932203</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0432522538986592</v>
+        <v>0.0485495648986301</v>
       </c>
       <c r="F5" t="n">
-        <v>0.231384615384615</v>
+        <v>0.235692307692308</v>
       </c>
       <c r="G5" t="s">
         <v>15</v>
@@ -985,19 +985,19 @@
         <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>32.8514715947981</v>
+        <v>0.303157894736842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.438947368421053</v>
+        <v>28.4681724845996</v>
       </c>
       <c r="K5" t="n">
-        <v>187</v>
+        <v>1736.84978990624</v>
       </c>
       <c r="L5" t="n">
-        <v>1551.32818047534</v>
+        <v>1594.38342349577</v>
       </c>
       <c r="M5" t="n">
-        <v>1618.90213645252</v>
+        <v>1574.35570090401</v>
       </c>
     </row>
     <row r="6">
@@ -1005,19 +1005,19 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>0.458769230769231</v>
+        <v>0.313230769230769</v>
       </c>
       <c r="D6" t="n">
-        <v>0.458769230769231</v>
+        <v>0.498095238095238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0431824185656474</v>
+        <v>0.0483450024237103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0412307692307692</v>
+        <v>0.186769230769231</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
@@ -1026,19 +1026,19 @@
         <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>31.958932238193</v>
+        <v>0.459649122807018</v>
       </c>
       <c r="J6" t="n">
-        <v>0.272982456140351</v>
+        <v>30.9924709103354</v>
       </c>
       <c r="K6" t="n">
-        <v>98</v>
+        <v>1414.25171716748</v>
       </c>
       <c r="L6" t="n">
-        <v>1581.73500270191</v>
+        <v>1557.96605530036</v>
       </c>
       <c r="M6" t="n">
-        <v>1706.83124302639</v>
+        <v>1660.82001426084</v>
       </c>
     </row>
     <row r="7">
@@ -1046,19 +1046,19 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>0.430153846153846</v>
+        <v>0.268615384615385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.430153846153846</v>
+        <v>0.443606557377049</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0406066793764023</v>
+        <v>0.0436113551064163</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0698461538461538</v>
+        <v>0.231384615384615</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -1067,27 +1067,27 @@
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>23.9288158795346</v>
+        <v>0.438947368421053</v>
       </c>
       <c r="J7" t="n">
-        <v>0.298947368421053</v>
+        <v>32.8514715947981</v>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>1334.39641407185</v>
       </c>
       <c r="L7" t="n">
-        <v>1478.44852737517</v>
+        <v>1618.90213645252</v>
       </c>
       <c r="M7" t="n">
-        <v>1533.32876556295</v>
+        <v>1551.32818047534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>0.328307692307692</v>
@@ -1096,7 +1096,7 @@
         <v>0.366440677966102</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0383973888916658</v>
+        <v>0.0405924287132591</v>
       </c>
       <c r="F8" t="n">
         <v>0.171692307692308</v>
@@ -1108,39 +1108,39 @@
         <v>16</v>
       </c>
       <c r="I8" t="n">
+        <v>0.379298245614035</v>
+      </c>
+      <c r="J8" t="n">
         <v>21.9383983572895</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.379298245614035</v>
-      </c>
       <c r="K8" t="n">
-        <v>52</v>
+        <v>1647.18255489636</v>
       </c>
       <c r="L8" t="n">
+        <v>1449.49034615022</v>
+      </c>
+      <c r="M8" t="n">
         <v>1546.53183415041</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1449.49034615022</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
       <c r="C9" t="n">
-        <v>0.201846153846154</v>
+        <v>0.430153846153846</v>
       </c>
       <c r="D9" t="n">
-        <v>0.375254237288136</v>
+        <v>0.430153846153846</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0351396232735952</v>
+        <v>0.0366340738309437</v>
       </c>
       <c r="F9" t="n">
-        <v>0.298153846153846</v>
+        <v>0.0698461538461538</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -1149,39 +1149,39 @@
         <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>27.3894592744695</v>
+        <v>0.298947368421053</v>
       </c>
       <c r="J9" t="n">
-        <v>0.388421052631579</v>
+        <v>23.9288158795346</v>
       </c>
       <c r="K9" t="n">
-        <v>173</v>
+        <v>1237.06064018222</v>
       </c>
       <c r="L9" t="n">
-        <v>1539.02370656006</v>
+        <v>1533.32876556295</v>
       </c>
       <c r="M9" t="n">
-        <v>1482.59610165319</v>
+        <v>1478.44852737517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
       <c r="C10" t="n">
-        <v>0.264307692307692</v>
+        <v>0.394461538461538</v>
       </c>
       <c r="D10" t="n">
-        <v>0.292881355932203</v>
+        <v>0.394461538461538</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0301916965100457</v>
+        <v>0.0287078699247201</v>
       </c>
       <c r="F10" t="n">
-        <v>0.235692307692308</v>
+        <v>0.105538461538462</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -1190,19 +1190,19 @@
         <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>28.4681724845996</v>
+        <v>0.263859649122807</v>
       </c>
       <c r="J10" t="n">
-        <v>0.303157894736842</v>
+        <v>25.4948665297741</v>
       </c>
       <c r="K10" t="n">
-        <v>47</v>
+        <v>1504.13671717247</v>
       </c>
       <c r="L10" t="n">
-        <v>1574.35570090401</v>
+        <v>1530.19865287729</v>
       </c>
       <c r="M10" t="n">
-        <v>1594.38342349577</v>
+        <v>1459.23100201067</v>
       </c>
     </row>
     <row r="11">
@@ -1213,16 +1213,16 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>0.394461538461538</v>
+        <v>0.201846153846154</v>
       </c>
       <c r="D11" t="n">
-        <v>0.394461538461538</v>
+        <v>0.375254237288136</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0299630176346778</v>
+        <v>0.0280472935558346</v>
       </c>
       <c r="F11" t="n">
-        <v>0.105538461538462</v>
+        <v>0.298153846153846</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -1231,19 +1231,19 @@
         <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>25.4948665297741</v>
+        <v>0.388421052631579</v>
       </c>
       <c r="J11" t="n">
-        <v>0.263859649122807</v>
+        <v>27.3894592744695</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>1514.23022738537</v>
       </c>
       <c r="L11" t="n">
-        <v>1459.23100201067</v>
+        <v>1482.59610165319</v>
       </c>
       <c r="M11" t="n">
-        <v>1530.19865287729</v>
+        <v>1539.02370656006</v>
       </c>
     </row>
     <row r="12">
@@ -1254,16 +1254,16 @@
         <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>0.292923076923077</v>
+        <v>0.256923076923077</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4515</v>
+        <v>0.256923076923077</v>
       </c>
       <c r="E12" t="n">
-        <v>0.024967123554212</v>
+        <v>0.0245174568637964</v>
       </c>
       <c r="F12" t="n">
-        <v>0.207076923076923</v>
+        <v>0.243076923076923</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -1272,19 +1272,19 @@
         <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>29.3935660506502</v>
+        <v>0.200350877192982</v>
       </c>
       <c r="J12" t="n">
-        <v>0.414035087719298</v>
+        <v>23.3839835728953</v>
       </c>
       <c r="K12" t="n">
-        <v>168</v>
+        <v>1662.01972011395</v>
       </c>
       <c r="L12" t="n">
-        <v>1538.36106658076</v>
+        <v>1453.38593690049</v>
       </c>
       <c r="M12" t="n">
-        <v>1475.0156284952</v>
+        <v>1570.56362801484</v>
       </c>
     </row>
     <row r="13">
@@ -1292,19 +1292,19 @@
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>0.382153846153846</v>
+        <v>0.292923076923077</v>
       </c>
       <c r="D13" t="n">
-        <v>0.382153846153846</v>
+        <v>0.4515</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0234567153416141</v>
+        <v>0.0237020200181272</v>
       </c>
       <c r="F13" t="n">
-        <v>0.117846153846154</v>
+        <v>0.207076923076923</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1313,39 +1313,39 @@
         <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>25.6892539356605</v>
+        <v>0.414035087719298</v>
       </c>
       <c r="J13" t="n">
-        <v>0.26280701754386</v>
+        <v>29.3935660506502</v>
       </c>
       <c r="K13" t="n">
-        <v>100</v>
+        <v>1625.26990086273</v>
       </c>
       <c r="L13" t="n">
-        <v>1491.6648444076</v>
+        <v>1475.0156284952</v>
       </c>
       <c r="M13" t="n">
-        <v>1486.59649552026</v>
+        <v>1538.36106658076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
-        <v>35</v>
-      </c>
       <c r="C14" t="n">
-        <v>0.256923076923077</v>
+        <v>0.382153846153846</v>
       </c>
       <c r="D14" t="n">
-        <v>0.256923076923077</v>
+        <v>0.382153846153846</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0210973249892518</v>
+        <v>0.0208225701409939</v>
       </c>
       <c r="F14" t="n">
-        <v>0.243076923076923</v>
+        <v>0.117846153846154</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1354,19 +1354,19 @@
         <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>23.3839835728953</v>
+        <v>0.26280701754386</v>
       </c>
       <c r="J14" t="n">
-        <v>0.200350877192982</v>
+        <v>25.6892539356605</v>
       </c>
       <c r="K14" t="n">
-        <v>42</v>
+        <v>1180.28259287132</v>
       </c>
       <c r="L14" t="n">
-        <v>1570.56362801484</v>
+        <v>1486.59649552026</v>
       </c>
       <c r="M14" t="n">
-        <v>1453.38593690049</v>
+        <v>1491.6648444076</v>
       </c>
     </row>
     <row r="15">
@@ -1374,19 +1374,19 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C15" t="n">
-        <v>0.322153846153846</v>
+        <v>0.273230769230769</v>
       </c>
       <c r="D15" t="n">
-        <v>0.322153846153846</v>
+        <v>0.273230769230769</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0195116870161994</v>
+        <v>0.0190874728052615</v>
       </c>
       <c r="F15" t="n">
-        <v>0.177846153846154</v>
+        <v>0.226769230769231</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1395,19 +1395,19 @@
         <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>29.5852156057495</v>
+        <v>0.278947368421053</v>
       </c>
       <c r="J15" t="n">
-        <v>0.12140350877193</v>
+        <v>24.8213552361396</v>
       </c>
       <c r="K15" t="n">
-        <v>165</v>
+        <v>1537.63177300895</v>
       </c>
       <c r="L15" t="n">
-        <v>1508.53955667597</v>
+        <v>1439.67316612083</v>
       </c>
       <c r="M15" t="n">
-        <v>1550.25575460791</v>
+        <v>1494.04324410132</v>
       </c>
     </row>
     <row r="16">
@@ -1415,19 +1415,19 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>0.332</v>
+        <v>0.228</v>
       </c>
       <c r="D16" t="n">
-        <v>0.332</v>
+        <v>0.271186440677966</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0193971658085814</v>
+        <v>0.017633093792141</v>
       </c>
       <c r="F16" t="n">
-        <v>0.168</v>
+        <v>0.272</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -1436,39 +1436,39 @@
         <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>23.6440793976728</v>
+        <v>0.280701754385965</v>
       </c>
       <c r="J16" t="n">
-        <v>0.105964912280702</v>
+        <v>32.7830253251198</v>
       </c>
       <c r="K16" t="n">
-        <v>96</v>
+        <v>1352.37217693764</v>
       </c>
       <c r="L16" t="n">
-        <v>1589.15219864359</v>
+        <v>1570.06715049991</v>
       </c>
       <c r="M16" t="n">
-        <v>1434.4081877527</v>
+        <v>1459.77099509582</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>0.273230769230769</v>
+        <v>0.259692307692308</v>
       </c>
       <c r="D17" t="n">
-        <v>0.273230769230769</v>
+        <v>0.332</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0174732674754469</v>
+        <v>0.0172431298199946</v>
       </c>
       <c r="F17" t="n">
-        <v>0.226769230769231</v>
+        <v>0.240307692307692</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1477,39 +1477,39 @@
         <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>24.8213552361396</v>
+        <v>0.32280701754386</v>
       </c>
       <c r="J17" t="n">
-        <v>0.278947368421053</v>
+        <v>29.242984257358</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>1748.96102326323</v>
       </c>
       <c r="L17" t="n">
-        <v>1494.04324410132</v>
+        <v>1433.44990356535</v>
       </c>
       <c r="M17" t="n">
-        <v>1439.67316612083</v>
+        <v>1599.66923571951</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>0.324923076923077</v>
+        <v>0.332</v>
       </c>
       <c r="D18" t="n">
-        <v>0.324923076923077</v>
+        <v>0.332</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0171724098013618</v>
+        <v>0.0166041453490894</v>
       </c>
       <c r="F18" t="n">
-        <v>0.175076923076923</v>
+        <v>0.168</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1518,19 +1518,19 @@
         <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>28.6762491444216</v>
+        <v>0.105964912280702</v>
       </c>
       <c r="J18" t="n">
-        <v>0.131578947368421</v>
+        <v>23.6440793976728</v>
       </c>
       <c r="K18" t="n">
-        <v>134</v>
+        <v>1488.28503086685</v>
       </c>
       <c r="L18" t="n">
-        <v>1450.44962245897</v>
+        <v>1434.4081877527</v>
       </c>
       <c r="M18" t="n">
-        <v>1544.05965084548</v>
+        <v>1589.15219864359</v>
       </c>
     </row>
     <row r="19">
@@ -1538,19 +1538,19 @@
         <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" t="n">
-        <v>0.228</v>
+        <v>0.324923076923077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.271186440677966</v>
+        <v>0.324923076923077</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0170842718101934</v>
+        <v>0.0164287343379477</v>
       </c>
       <c r="F19" t="n">
-        <v>0.272</v>
+        <v>0.175076923076923</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1559,19 +1559,19 @@
         <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>32.7830253251198</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="J19" t="n">
-        <v>0.280701754385965</v>
+        <v>28.6762491444216</v>
       </c>
       <c r="K19" t="n">
-        <v>165</v>
+        <v>1613.30577373982</v>
       </c>
       <c r="L19" t="n">
-        <v>1459.77099509582</v>
+        <v>1544.05965084548</v>
       </c>
       <c r="M19" t="n">
-        <v>1570.06715049991</v>
+        <v>1450.44962245897</v>
       </c>
     </row>
     <row r="20">
@@ -1579,19 +1579,19 @@
         <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.259692307692308</v>
+        <v>0.322153846153846</v>
       </c>
       <c r="D20" t="n">
-        <v>0.332</v>
+        <v>0.322153846153846</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0149972279718202</v>
+        <v>0.015716059483184</v>
       </c>
       <c r="F20" t="n">
-        <v>0.240307692307692</v>
+        <v>0.177846153846154</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1600,19 +1600,19 @@
         <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>29.242984257358</v>
+        <v>0.12140350877193</v>
       </c>
       <c r="J20" t="n">
-        <v>0.32280701754386</v>
+        <v>29.5852156057495</v>
       </c>
       <c r="K20" t="n">
-        <v>131</v>
+        <v>1230.64497943139</v>
       </c>
       <c r="L20" t="n">
-        <v>1599.66923571951</v>
+        <v>1550.25575460791</v>
       </c>
       <c r="M20" t="n">
-        <v>1433.44990356535</v>
+        <v>1508.53955667597</v>
       </c>
     </row>
     <row r="21">
@@ -1620,7 +1620,7 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
         <v>0.208307692307692</v>
@@ -1629,7 +1629,7 @@
         <v>0.208307692307692</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0146675711862375</v>
+        <v>0.0154620299831641</v>
       </c>
       <c r="F21" t="n">
         <v>0.291692307692308</v>
@@ -1641,19 +1641,19 @@
         <v>16</v>
       </c>
       <c r="I21" t="n">
+        <v>0.10280701754386</v>
+      </c>
+      <c r="J21" t="n">
         <v>23.5893223819302</v>
       </c>
-      <c r="J21" t="n">
-        <v>0.10280701754386</v>
-      </c>
       <c r="K21" t="n">
-        <v>51</v>
+        <v>1625.23203644872</v>
       </c>
       <c r="L21" t="n">
+        <v>1453.59156162036</v>
+      </c>
+      <c r="M21" t="n">
         <v>1486.65969153085</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1453.59156162036</v>
       </c>
     </row>
     <row r="22">
@@ -1661,19 +1661,19 @@
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
-        <v>0.370153846153846</v>
+        <v>0.119384615384615</v>
       </c>
       <c r="D22" t="n">
-        <v>0.370153846153846</v>
+        <v>0.16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0139612169969272</v>
+        <v>0.0139955690948073</v>
       </c>
       <c r="F22" t="n">
-        <v>0.129846153846154</v>
+        <v>0.380615384615385</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
@@ -1682,39 +1682,39 @@
         <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>24.72553045859</v>
+        <v>0.165614035087719</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0936842105263158</v>
+        <v>27.2142368240931</v>
       </c>
       <c r="K22" t="n">
-        <v>71</v>
+        <v>1553.49247004466</v>
       </c>
       <c r="L22" t="n">
-        <v>1513.75700783214</v>
+        <v>1496.09960808685</v>
       </c>
       <c r="M22" t="n">
-        <v>1455.09425401236</v>
+        <v>1423.47586303</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.260307692307692</v>
+        <v>0.327076923076923</v>
       </c>
       <c r="D23" t="n">
-        <v>0.299322033898305</v>
+        <v>0.327076923076923</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0123594492685416</v>
+        <v>0.0137440779693313</v>
       </c>
       <c r="F23" t="n">
-        <v>0.239692307692308</v>
+        <v>0.172923076923077</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1723,39 +1723,39 @@
         <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>34.031485284052</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.309824561403509</v>
+        <v>30.5681040383299</v>
       </c>
       <c r="K23" t="n">
-        <v>326</v>
+        <v>1700.13881527886</v>
       </c>
       <c r="L23" t="n">
-        <v>1492.02337886906</v>
+        <v>1548.69590538699</v>
       </c>
       <c r="M23" t="n">
-        <v>1417.83820576077</v>
+        <v>1580.14078674673</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>0.103076923076923</v>
+        <v>0.370153846153846</v>
       </c>
       <c r="D24" t="n">
-        <v>0.160338983050847</v>
+        <v>0.370153846153846</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0116173932182673</v>
+        <v>0.013321214692126</v>
       </c>
       <c r="F24" t="n">
-        <v>0.396923076923077</v>
+        <v>0.129846153846154</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -1764,27 +1764,27 @@
         <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>22.8281998631075</v>
+        <v>0.0936842105263158</v>
       </c>
       <c r="J24" t="n">
-        <v>0.165964912280702</v>
+        <v>24.72553045859</v>
       </c>
       <c r="K24" t="n">
-        <v>32</v>
+        <v>1315.39153301769</v>
       </c>
       <c r="L24" t="n">
-        <v>1397.2343995728</v>
+        <v>1455.09425401236</v>
       </c>
       <c r="M24" t="n">
-        <v>1418.09250811081</v>
+        <v>1513.75700783214</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C25" t="n">
         <v>0.225846153846154</v>
@@ -1793,7 +1793,7 @@
         <v>0.238095238095238</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0110700503900684</v>
+        <v>0.0131945254822884</v>
       </c>
       <c r="F25" t="n">
         <v>0.274153846153846</v>
@@ -1805,39 +1805,39 @@
         <v>16</v>
       </c>
       <c r="I25" t="n">
+        <v>0.167719298245614</v>
+      </c>
+      <c r="J25" t="n">
         <v>29.138945927447</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.167719298245614</v>
-      </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>1626.9578661762</v>
       </c>
       <c r="L25" t="n">
+        <v>1481.1096391574</v>
+      </c>
+      <c r="M25" t="n">
         <v>1520.08673618446</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1481.1096391574</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
-        <v>0.321538461538462</v>
+        <v>0.190461538461538</v>
       </c>
       <c r="D26" t="n">
-        <v>0.321538461538462</v>
+        <v>0.190461538461538</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0109330965052173</v>
+        <v>0.0124981829357413</v>
       </c>
       <c r="F26" t="n">
-        <v>0.178461538461538</v>
+        <v>0.309538461538462</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
@@ -1846,39 +1846,39 @@
         <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>27.750855578371</v>
+        <v>0.0839344262295082</v>
       </c>
       <c r="J26" t="n">
-        <v>0.13859649122807</v>
+        <v>27.5920602327173</v>
       </c>
       <c r="K26" t="n">
-        <v>124</v>
+        <v>1382.85841537607</v>
       </c>
       <c r="L26" t="n">
-        <v>1413.47560180465</v>
+        <v>1514.67244911738</v>
       </c>
       <c r="M26" t="n">
-        <v>1468.80824684596</v>
+        <v>1445.05026589174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C27" t="n">
-        <v>0.119384615384615</v>
+        <v>0.103076923076923</v>
       </c>
       <c r="D27" t="n">
-        <v>0.16</v>
+        <v>0.160338983050847</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0107297934126658</v>
+        <v>0.0122479766153823</v>
       </c>
       <c r="F27" t="n">
-        <v>0.380615384615385</v>
+        <v>0.396923076923077</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1887,27 +1887,27 @@
         <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>27.2142368240931</v>
+        <v>0.165964912280702</v>
       </c>
       <c r="J27" t="n">
-        <v>0.165614035087719</v>
+        <v>22.8281998631075</v>
       </c>
       <c r="K27" t="n">
-        <v>47</v>
+        <v>1512.75771811409</v>
       </c>
       <c r="L27" t="n">
-        <v>1423.47586303</v>
+        <v>1418.09250811081</v>
       </c>
       <c r="M27" t="n">
-        <v>1496.09960808685</v>
+        <v>1397.2343995728</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
         <v>0.228</v>
@@ -1916,7 +1916,7 @@
         <v>0.228</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0104899720046327</v>
+        <v>0.0105631703366651</v>
       </c>
       <c r="F28" t="n">
         <v>0.272</v>
@@ -1928,39 +1928,39 @@
         <v>16</v>
       </c>
       <c r="I28" t="n">
+        <v>0.110877192982456</v>
+      </c>
+      <c r="J28" t="n">
         <v>24.5284052019165</v>
       </c>
-      <c r="J28" t="n">
-        <v>0.110877192982456</v>
-      </c>
       <c r="K28" t="n">
-        <v>55</v>
+        <v>1417.96308206404</v>
       </c>
       <c r="L28" t="n">
+        <v>1445.3162988372</v>
+      </c>
+      <c r="M28" t="n">
         <v>1401.36886950135</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1445.3162988372</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C29" t="n">
-        <v>0.190461538461538</v>
+        <v>0.245230769230769</v>
       </c>
       <c r="D29" t="n">
-        <v>0.190461538461538</v>
+        <v>0.245230769230769</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00969044218198883</v>
+        <v>0.00986243010447593</v>
       </c>
       <c r="F29" t="n">
-        <v>0.309538461538462</v>
+        <v>0.254769230769231</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1969,39 +1969,39 @@
         <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>27.5920602327173</v>
+        <v>0.111746031746032</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0839344262295082</v>
+        <v>27.958932238193</v>
       </c>
       <c r="K29" t="n">
-        <v>42</v>
+        <v>1387.35175948227</v>
       </c>
       <c r="L29" t="n">
-        <v>1445.05026589174</v>
+        <v>1435.3200807196</v>
       </c>
       <c r="M29" t="n">
-        <v>1514.67244911738</v>
+        <v>1561.52630943399</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>0.276307692307692</v>
+        <v>0.112</v>
       </c>
       <c r="D30" t="n">
-        <v>0.276307692307692</v>
+        <v>0.27</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00960604798599443</v>
+        <v>0.00945762479220109</v>
       </c>
       <c r="F30" t="n">
-        <v>0.223692307692308</v>
+        <v>0.388</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -2010,39 +2010,39 @@
         <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>21.242984257358</v>
+        <v>0.302222222222222</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>32.9199178644764</v>
       </c>
       <c r="K30" t="n">
-        <v>36</v>
+        <v>1463.87324822627</v>
       </c>
       <c r="L30" t="n">
-        <v>1425.1416315827</v>
+        <v>1458.84057221738</v>
       </c>
       <c r="M30" t="n">
-        <v>1394.7948090508</v>
+        <v>1484.83959719207</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>0.327076923076923</v>
+        <v>0.321538461538462</v>
       </c>
       <c r="D31" t="n">
-        <v>0.327076923076923</v>
+        <v>0.321538461538462</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0093844968958303</v>
+        <v>0.00932330425225811</v>
       </c>
       <c r="F31" t="n">
-        <v>0.172923076923077</v>
+        <v>0.178461538461538</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -2051,39 +2051,39 @@
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>30.5681040383299</v>
+        <v>0.13859649122807</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>27.750855578371</v>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
+        <v>1257.09062409593</v>
       </c>
       <c r="L31" t="n">
-        <v>1580.14078674673</v>
+        <v>1468.80824684596</v>
       </c>
       <c r="M31" t="n">
-        <v>1548.69590538699</v>
+        <v>1413.47560180465</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C32" t="n">
-        <v>0.111384615384615</v>
+        <v>0.276307692307692</v>
       </c>
       <c r="D32" t="n">
-        <v>0.379047619047619</v>
+        <v>0.276307692307692</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00840877890737376</v>
+        <v>0.00852171451268553</v>
       </c>
       <c r="F32" t="n">
-        <v>0.388615384615385</v>
+        <v>0.223692307692308</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -2092,39 +2092,39 @@
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>28.5201916495551</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.129473684210526</v>
+        <v>21.242984257358</v>
       </c>
       <c r="K32" t="n">
-        <v>174</v>
+        <v>1432.6155584565</v>
       </c>
       <c r="L32" t="n">
-        <v>1372.62411856363</v>
+        <v>1394.7948090508</v>
       </c>
       <c r="M32" t="n">
-        <v>1427.38513470566</v>
+        <v>1425.1416315827</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.112</v>
+        <v>0.217846153846154</v>
       </c>
       <c r="D33" t="n">
-        <v>0.27</v>
+        <v>0.217846153846154</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00803778376630174</v>
+        <v>0.00817418240999972</v>
       </c>
       <c r="F33" t="n">
-        <v>0.388</v>
+        <v>0.282153846153846</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -2133,39 +2133,39 @@
         <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>32.9199178644764</v>
+        <v>0.219298245614035</v>
       </c>
       <c r="J33" t="n">
-        <v>0.302222222222222</v>
+        <v>28.2053388090349</v>
       </c>
       <c r="K33" t="n">
-        <v>147</v>
+        <v>1232.31786737431</v>
       </c>
       <c r="L33" t="n">
-        <v>1484.83959719207</v>
+        <v>1391.88816692229</v>
       </c>
       <c r="M33" t="n">
-        <v>1458.84057221738</v>
+        <v>1518.35942120275</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C34" t="n">
-        <v>0.217846153846154</v>
+        <v>0.361230769230769</v>
       </c>
       <c r="D34" t="n">
-        <v>0.217846153846154</v>
+        <v>0.361230769230769</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00772345268145326</v>
+        <v>0.00810829148490344</v>
       </c>
       <c r="F34" t="n">
-        <v>0.282153846153846</v>
+        <v>0.138769230769231</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -2174,39 +2174,39 @@
         <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>28.2053388090349</v>
+        <v>0.204561403508772</v>
       </c>
       <c r="J34" t="n">
-        <v>0.219298245614035</v>
+        <v>32.0191649555099</v>
       </c>
       <c r="K34" t="n">
-        <v>95</v>
+        <v>1621.44565381508</v>
       </c>
       <c r="L34" t="n">
-        <v>1518.35942120275</v>
+        <v>1448.18714069982</v>
       </c>
       <c r="M34" t="n">
-        <v>1391.88816692229</v>
+        <v>1496.96789848146</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C35" t="n">
-        <v>0.170461538461538</v>
+        <v>0.143384615384615</v>
       </c>
       <c r="D35" t="n">
-        <v>0.170461538461538</v>
+        <v>0.143384615384615</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00743210225729623</v>
+        <v>0.00707590483694574</v>
       </c>
       <c r="F35" t="n">
-        <v>0.329538461538462</v>
+        <v>0.356615384615385</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -2215,39 +2215,39 @@
         <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>24.4709103353867</v>
+        <v>0.139298245614035</v>
       </c>
       <c r="J35" t="n">
-        <v>0.128070175438597</v>
+        <v>23.895961670089</v>
       </c>
       <c r="K35" t="n">
-        <v>67</v>
+        <v>1429.89699827518</v>
       </c>
       <c r="L35" t="n">
-        <v>1400.28682568561</v>
+        <v>1345.6061901977</v>
       </c>
       <c r="M35" t="n">
-        <v>1378.34616629367</v>
+        <v>1458.97823254735</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>0.143384615384615</v>
+        <v>0.170461538461538</v>
       </c>
       <c r="D36" t="n">
-        <v>0.143384615384615</v>
+        <v>0.170461538461538</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00738868759877024</v>
+        <v>0.00688954515134266</v>
       </c>
       <c r="F36" t="n">
-        <v>0.356615384615385</v>
+        <v>0.329538461538462</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2256,39 +2256,39 @@
         <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>23.895961670089</v>
+        <v>0.128070175438597</v>
       </c>
       <c r="J36" t="n">
-        <v>0.139298245614035</v>
+        <v>24.4709103353867</v>
       </c>
       <c r="K36" t="n">
-        <v>63</v>
+        <v>1332.88975458566</v>
       </c>
       <c r="L36" t="n">
-        <v>1458.97823254735</v>
+        <v>1378.34616629367</v>
       </c>
       <c r="M36" t="n">
-        <v>1345.6061901977</v>
+        <v>1400.28682568561</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>0.361230769230769</v>
+        <v>0.151076923076923</v>
       </c>
       <c r="D37" t="n">
-        <v>0.361230769230769</v>
+        <v>0.319661016949153</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00665653709859512</v>
+        <v>0.00663931746516016</v>
       </c>
       <c r="F37" t="n">
-        <v>0.138769230769231</v>
+        <v>0.348923076923077</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
@@ -2297,39 +2297,39 @@
         <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>32.0191649555099</v>
+        <v>0.330877192982456</v>
       </c>
       <c r="J37" t="n">
-        <v>0.204561403508772</v>
+        <v>32.5913757700205</v>
       </c>
       <c r="K37" t="n">
-        <v>132</v>
+        <v>1571.15388863315</v>
       </c>
       <c r="L37" t="n">
-        <v>1496.96789848146</v>
+        <v>1382.92779213082</v>
       </c>
       <c r="M37" t="n">
-        <v>1448.18714069982</v>
+        <v>1495.83524497121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C38" t="n">
-        <v>0.245230769230769</v>
+        <v>0.141538461538462</v>
       </c>
       <c r="D38" t="n">
-        <v>0.245230769230769</v>
+        <v>0.1485</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00664053661435022</v>
+        <v>0.00636550293659653</v>
       </c>
       <c r="F38" t="n">
-        <v>0.254769230769231</v>
+        <v>0.358461538461538</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -2338,39 +2338,39 @@
         <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>27.958932238193</v>
+        <v>0.174705882352941</v>
       </c>
       <c r="J38" t="n">
-        <v>0.111746031746032</v>
+        <v>26.1629021218344</v>
       </c>
       <c r="K38" t="n">
-        <v>27</v>
+        <v>1225.6837219819</v>
       </c>
       <c r="L38" t="n">
-        <v>1561.52630943399</v>
+        <v>1382.65421457658</v>
       </c>
       <c r="M38" t="n">
-        <v>1435.3200807196</v>
+        <v>1391.87090296566</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" t="s">
         <v>64</v>
       </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
       <c r="C39" t="n">
-        <v>0.185230769230769</v>
+        <v>0.260307692307692</v>
       </c>
       <c r="D39" t="n">
-        <v>0.185230769230769</v>
+        <v>0.299322033898305</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00623192698096693</v>
+        <v>0.00630059765323624</v>
       </c>
       <c r="F39" t="n">
-        <v>0.314769230769231</v>
+        <v>0.239692307692308</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
@@ -2379,19 +2379,19 @@
         <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>22.7953456536619</v>
+        <v>0.309824561403509</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>34.031485284052</v>
       </c>
       <c r="K39" t="n">
-        <v>37</v>
+        <v>1279.4212895648</v>
       </c>
       <c r="L39" t="n">
-        <v>1397.19113826149</v>
+        <v>1417.83820576077</v>
       </c>
       <c r="M39" t="n">
-        <v>1375.68441167262</v>
+        <v>1492.02337886906</v>
       </c>
     </row>
     <row r="40">
@@ -2399,19 +2399,19 @@
         <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C40" t="n">
-        <v>0.151076923076923</v>
+        <v>0.111384615384615</v>
       </c>
       <c r="D40" t="n">
-        <v>0.319661016949153</v>
+        <v>0.379047619047619</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00599911619478557</v>
+        <v>0.00620960432357408</v>
       </c>
       <c r="F40" t="n">
-        <v>0.348923076923077</v>
+        <v>0.388615384615385</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
@@ -2420,19 +2420,19 @@
         <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>32.5913757700205</v>
+        <v>0.129473684210526</v>
       </c>
       <c r="J40" t="n">
-        <v>0.330877192982456</v>
+        <v>28.5201916495551</v>
       </c>
       <c r="K40" t="n">
-        <v>163</v>
+        <v>1534.86862199725</v>
       </c>
       <c r="L40" t="n">
-        <v>1495.83524497121</v>
+        <v>1427.38513470566</v>
       </c>
       <c r="M40" t="n">
-        <v>1382.92779213082</v>
+        <v>1372.62411856363</v>
       </c>
     </row>
     <row r="41">
@@ -2440,7 +2440,7 @@
         <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C41" t="n">
         <v>0.136307692307692</v>
@@ -2449,7 +2449,7 @@
         <v>0.152203389830508</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00584703280529628</v>
+        <v>0.00591011905663496</v>
       </c>
       <c r="F41" t="n">
         <v>0.363692307692308</v>
@@ -2461,19 +2461,19 @@
         <v>16</v>
       </c>
       <c r="I41" t="n">
+        <v>0.157543859649123</v>
+      </c>
+      <c r="J41" t="n">
         <v>27.7837097878166</v>
       </c>
-      <c r="J41" t="n">
-        <v>0.157543859649123</v>
-      </c>
       <c r="K41" t="n">
-        <v>80</v>
+        <v>1250.49310922027</v>
       </c>
       <c r="L41" t="n">
+        <v>1435.6030759549</v>
+      </c>
+      <c r="M41" t="n">
         <v>1293.83928252634</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1435.6030759549</v>
       </c>
     </row>
     <row r="42">
@@ -2481,19 +2481,19 @@
         <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C42" t="n">
-        <v>0.141538461538462</v>
+        <v>0.185230769230769</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1485</v>
+        <v>0.185230769230769</v>
       </c>
       <c r="E42" t="n">
-        <v>0.00573689466349716</v>
+        <v>0.00590645667008197</v>
       </c>
       <c r="F42" t="n">
-        <v>0.358461538461538</v>
+        <v>0.314769230769231</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2502,19 +2502,19 @@
         <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>26.1629021218344</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.174705882352941</v>
+        <v>22.7953456536619</v>
       </c>
       <c r="K42" t="n">
-        <v>47</v>
+        <v>1395.8408309069</v>
       </c>
       <c r="L42" t="n">
-        <v>1391.87090296566</v>
+        <v>1375.68441167262</v>
       </c>
       <c r="M42" t="n">
-        <v>1382.65421457658</v>
+        <v>1397.19113826149</v>
       </c>
     </row>
     <row r="43">
@@ -2522,7 +2522,7 @@
         <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C43" t="n">
         <v>0.152</v>
@@ -2531,7 +2531,7 @@
         <v>0.152</v>
       </c>
       <c r="E43" t="n">
-        <v>0.00571479186508664</v>
+        <v>0.00587676216272052</v>
       </c>
       <c r="F43" t="n">
         <v>0.348</v>
@@ -2543,19 +2543,19 @@
         <v>16</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>24.7145790554415</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
       <c r="K43" t="n">
-        <v>35</v>
+        <v>1262.42636883388</v>
       </c>
       <c r="L43" t="n">
+        <v>1420.01934609008</v>
+      </c>
+      <c r="M43" t="n">
         <v>1367.45225942492</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1420.01934609008</v>
       </c>
     </row>
     <row r="44">
@@ -2563,19 +2563,19 @@
         <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0972307692307692</v>
+        <v>0.155692307692308</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2095</v>
+        <v>0.163728813559322</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00557073178078686</v>
+        <v>0.0055159799185473</v>
       </c>
       <c r="F44" t="n">
-        <v>0.402769230769231</v>
+        <v>0.344307692307692</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -2584,19 +2584,19 @@
         <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>26.7789185489391</v>
+        <v>0.169473684210526</v>
       </c>
       <c r="J44" t="n">
-        <v>0.113333333333333</v>
+        <v>25.388090349076</v>
       </c>
       <c r="K44" t="n">
-        <v>117</v>
+        <v>1544.14382366596</v>
       </c>
       <c r="L44" t="n">
-        <v>1315.59993754028</v>
+        <v>1311.05307312204</v>
       </c>
       <c r="M44" t="n">
-        <v>1385.55668527546</v>
+        <v>1475.280550107</v>
       </c>
     </row>
     <row r="45">
@@ -2604,19 +2604,19 @@
         <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
-        <v>0.117230769230769</v>
+        <v>0.171076923076923</v>
       </c>
       <c r="D45" t="n">
-        <v>0.117230769230769</v>
+        <v>0.171076923076923</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00496056045514416</v>
+        <v>0.00516982656614473</v>
       </c>
       <c r="F45" t="n">
-        <v>0.382769230769231</v>
+        <v>0.328923076923077</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
@@ -2625,19 +2625,19 @@
         <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>24.4873374401095</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0845614035087719</v>
+        <v>27.4250513347023</v>
       </c>
       <c r="K45" t="n">
-        <v>29</v>
+        <v>1301.72375343194</v>
       </c>
       <c r="L45" t="n">
-        <v>1320.55160751415</v>
+        <v>1432.72524617131</v>
       </c>
       <c r="M45" t="n">
-        <v>1382.98346396969</v>
+        <v>1394.62367979902</v>
       </c>
     </row>
     <row r="46">
@@ -2645,19 +2645,19 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C46" t="n">
-        <v>0.124923076923077</v>
+        <v>0.117230769230769</v>
       </c>
       <c r="D46" t="n">
-        <v>0.124923076923077</v>
+        <v>0.117230769230769</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00468436608058189</v>
+        <v>0.00513977264066718</v>
       </c>
       <c r="F46" t="n">
-        <v>0.375076923076923</v>
+        <v>0.382769230769231</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
@@ -2666,19 +2666,19 @@
         <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>22.8418891170431</v>
+        <v>0.0845614035087719</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>24.4873374401095</v>
       </c>
       <c r="K46" t="n">
-        <v>24</v>
+        <v>1214.16162024139</v>
       </c>
       <c r="L46" t="n">
-        <v>1378.14921120525</v>
+        <v>1382.98346396969</v>
       </c>
       <c r="M46" t="n">
-        <v>1349.05057356984</v>
+        <v>1320.55160751415</v>
       </c>
     </row>
     <row r="47">
@@ -2686,19 +2686,19 @@
         <v>72</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C47" t="n">
-        <v>0.155692307692308</v>
+        <v>0.124923076923077</v>
       </c>
       <c r="D47" t="n">
-        <v>0.163728813559322</v>
+        <v>0.124923076923077</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00468082447171685</v>
+        <v>0.00483545904873934</v>
       </c>
       <c r="F47" t="n">
-        <v>0.344307692307692</v>
+        <v>0.375076923076923</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
@@ -2707,19 +2707,19 @@
         <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>25.388090349076</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.169473684210526</v>
+        <v>22.8418891170431</v>
       </c>
       <c r="K47" t="n">
-        <v>47</v>
+        <v>1508.73473992406</v>
       </c>
       <c r="L47" t="n">
-        <v>1475.280550107</v>
+        <v>1349.05057356984</v>
       </c>
       <c r="M47" t="n">
-        <v>1311.05307312204</v>
+        <v>1378.14921120525</v>
       </c>
     </row>
     <row r="48">
@@ -2727,19 +2727,19 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0723076923076923</v>
+        <v>0.115076923076923</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0723076923076923</v>
+        <v>0.115076923076923</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00467903478093652</v>
+        <v>0.00472091842123389</v>
       </c>
       <c r="F48" t="n">
-        <v>0.427692307692308</v>
+        <v>0.384923076923077</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
@@ -2748,19 +2748,19 @@
         <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>22.8692676249144</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>23.0280629705681</v>
       </c>
       <c r="K48" t="n">
-        <v>18</v>
+        <v>1489.4012128709</v>
       </c>
       <c r="L48" t="n">
-        <v>1290.86945317176</v>
+        <v>1341.25980770169</v>
       </c>
       <c r="M48" t="n">
-        <v>1378.88729757936</v>
+        <v>1401.47383286135</v>
       </c>
     </row>
     <row r="49">
@@ -2768,19 +2768,19 @@
         <v>74</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C49" t="n">
-        <v>0.101538461538462</v>
+        <v>0.0723076923076923</v>
       </c>
       <c r="D49" t="n">
-        <v>0.101538461538462</v>
+        <v>0.0723076923076923</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00462498633059976</v>
+        <v>0.00469289582066904</v>
       </c>
       <c r="F49" t="n">
-        <v>0.398461538461538</v>
+        <v>0.427692307692308</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
@@ -2789,19 +2789,19 @@
         <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>22.7542778918549</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>22.8692676249144</v>
       </c>
       <c r="K49" t="n">
-        <v>30</v>
+        <v>1395.67989451059</v>
       </c>
       <c r="L49" t="n">
-        <v>1355.10121362168</v>
+        <v>1378.88729757936</v>
       </c>
       <c r="M49" t="n">
-        <v>1347.30257201768</v>
+        <v>1290.86945317176</v>
       </c>
     </row>
     <row r="50">
@@ -2809,19 +2809,19 @@
         <v>75</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
-        <v>0.072</v>
+        <v>0.139076923076923</v>
       </c>
       <c r="D50" t="n">
-        <v>0.072</v>
+        <v>0.139076923076923</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00442181945003817</v>
+        <v>0.00463316549973235</v>
       </c>
       <c r="F50" t="n">
-        <v>0.428</v>
+        <v>0.360923076923077</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2830,19 +2830,19 @@
         <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>22.4421629021218</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>23.9069130732375</v>
       </c>
       <c r="K50" t="n">
-        <v>13</v>
+        <v>1500.95317698071</v>
       </c>
       <c r="L50" t="n">
-        <v>1352.8010955241</v>
+        <v>1356.45929364849</v>
       </c>
       <c r="M50" t="n">
-        <v>1345.76044819342</v>
+        <v>1387.62707309998</v>
       </c>
     </row>
     <row r="51">
@@ -2850,19 +2850,19 @@
         <v>76</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C51" t="n">
-        <v>0.104</v>
+        <v>0.101538461538462</v>
       </c>
       <c r="D51" t="n">
-        <v>0.104</v>
+        <v>0.101538461538462</v>
       </c>
       <c r="E51" t="n">
-        <v>0.00441957259013171</v>
+        <v>0.00451288405218685</v>
       </c>
       <c r="F51" t="n">
-        <v>0.396</v>
+        <v>0.398461538461538</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -2871,19 +2871,19 @@
         <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>20.5913757700205</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>22.7542778918549</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
+        <v>1455.93679998291</v>
       </c>
       <c r="L51" t="n">
-        <v>1210.97472684585</v>
+        <v>1347.30257201768</v>
       </c>
       <c r="M51" t="n">
-        <v>1323.558085724</v>
+        <v>1355.10121362168</v>
       </c>
     </row>
     <row r="52">
@@ -2891,19 +2891,19 @@
         <v>77</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C52" t="n">
-        <v>0.115076923076923</v>
+        <v>0.0972307692307692</v>
       </c>
       <c r="D52" t="n">
-        <v>0.115076923076923</v>
+        <v>0.2095</v>
       </c>
       <c r="E52" t="n">
-        <v>0.00438055723160941</v>
+        <v>0.00450993852943132</v>
       </c>
       <c r="F52" t="n">
-        <v>0.384923076923077</v>
+        <v>0.402769230769231</v>
       </c>
       <c r="G52" t="s">
         <v>15</v>
@@ -2912,19 +2912,19 @@
         <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>23.0280629705681</v>
+        <v>0.113333333333333</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>26.7789185489391</v>
       </c>
       <c r="K52" t="n">
-        <v>18</v>
+        <v>1343.51438286255</v>
       </c>
       <c r="L52" t="n">
-        <v>1401.47383286135</v>
+        <v>1385.55668527546</v>
       </c>
       <c r="M52" t="n">
-        <v>1341.25980770169</v>
+        <v>1315.59993754028</v>
       </c>
     </row>
     <row r="53">
@@ -2932,19 +2932,19 @@
         <v>78</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0584615384615385</v>
+        <v>0.072</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0584615384615385</v>
+        <v>0.072</v>
       </c>
       <c r="E53" t="n">
-        <v>0.00437752351884367</v>
+        <v>0.00447616353317436</v>
       </c>
       <c r="F53" t="n">
-        <v>0.441538461538462</v>
+        <v>0.428</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -2953,19 +2953,19 @@
         <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>22.7734428473648</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>22.4421629021218</v>
       </c>
       <c r="K53" t="n">
-        <v>25</v>
+        <v>1356.83697567042</v>
       </c>
       <c r="L53" t="n">
-        <v>1358.44226778984</v>
+        <v>1345.76044819342</v>
       </c>
       <c r="M53" t="n">
-        <v>1342.20853986321</v>
+        <v>1352.8010955241</v>
       </c>
     </row>
     <row r="54">
@@ -2973,19 +2973,19 @@
         <v>79</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0846153846153846</v>
+        <v>0.0584615384615385</v>
       </c>
       <c r="D54" t="n">
-        <v>0.198</v>
+        <v>0.0584615384615385</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00437297257979393</v>
+        <v>0.00426067637817385</v>
       </c>
       <c r="F54" t="n">
-        <v>0.415384615384615</v>
+        <v>0.441538461538462</v>
       </c>
       <c r="G54" t="s">
         <v>15</v>
@@ -2994,19 +2994,19 @@
         <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>33.9739904175222</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.232941176470588</v>
+        <v>22.7734428473648</v>
       </c>
       <c r="K54" t="n">
-        <v>250</v>
+        <v>1344.69426837203</v>
       </c>
       <c r="L54" t="n">
-        <v>1365.90879169601</v>
+        <v>1342.20853986321</v>
       </c>
       <c r="M54" t="n">
-        <v>1377.33444148005</v>
+        <v>1358.44226778984</v>
       </c>
     </row>
     <row r="55">
@@ -3014,19 +3014,19 @@
         <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0772307692307692</v>
+        <v>0.110769230769231</v>
       </c>
       <c r="D55" t="n">
-        <v>0.126</v>
+        <v>0.1275</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00430959681783034</v>
+        <v>0.00393538586625176</v>
       </c>
       <c r="F55" t="n">
-        <v>0.422769230769231</v>
+        <v>0.389230769230769</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
@@ -3035,39 +3035,39 @@
         <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>22.9295003422313</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0873684210526316</v>
+        <v>27.6577686516085</v>
       </c>
       <c r="K55" t="n">
-        <v>61</v>
+        <v>1150.37812819264</v>
       </c>
       <c r="L55" t="n">
-        <v>1270.97275630001</v>
+        <v>1350.13497245266</v>
       </c>
       <c r="M55" t="n">
-        <v>1313.99836675921</v>
+        <v>1403.04482404585</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C56" t="n">
-        <v>0.110769230769231</v>
+        <v>0.0526153846153846</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1275</v>
+        <v>0.122380952380952</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00423110372583075</v>
+        <v>0.00365598339236754</v>
       </c>
       <c r="F56" t="n">
-        <v>0.389230769230769</v>
+        <v>0.447384615384615</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
@@ -3076,19 +3076,19 @@
         <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>27.6577686516085</v>
+        <v>0.108421052631579</v>
       </c>
       <c r="J56" t="n">
-        <v>0.131578947368421</v>
+        <v>28.6789869952088</v>
       </c>
       <c r="K56" t="n">
-        <v>96</v>
+        <v>1466.60561581011</v>
       </c>
       <c r="L56" t="n">
-        <v>1403.04482404585</v>
+        <v>1355.27921646996</v>
       </c>
       <c r="M56" t="n">
-        <v>1350.13497245266</v>
+        <v>1392.88707384781</v>
       </c>
     </row>
     <row r="57">
@@ -3096,19 +3096,19 @@
         <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C57" t="n">
-        <v>0.139076923076923</v>
+        <v>0.0929230769230769</v>
       </c>
       <c r="D57" t="n">
-        <v>0.139076923076923</v>
+        <v>0.104406779661017</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00418371931559436</v>
+        <v>0.00360612035596816</v>
       </c>
       <c r="F57" t="n">
-        <v>0.360923076923077</v>
+        <v>0.407076923076923</v>
       </c>
       <c r="G57" t="s">
         <v>15</v>
@@ -3117,19 +3117,19 @@
         <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>23.9069130732375</v>
+        <v>0.108070175438596</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>26.6475017111567</v>
       </c>
       <c r="K57" t="n">
-        <v>23</v>
+        <v>1468.74951489673</v>
       </c>
       <c r="L57" t="n">
-        <v>1387.62707309998</v>
+        <v>1350.91736681457</v>
       </c>
       <c r="M57" t="n">
-        <v>1356.45929364849</v>
+        <v>1306.24531691601</v>
       </c>
     </row>
     <row r="58">
@@ -3137,19 +3137,19 @@
         <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C58" t="n">
-        <v>0.171076923076923</v>
+        <v>0.114769230769231</v>
       </c>
       <c r="D58" t="n">
-        <v>0.171076923076923</v>
+        <v>0.114769230769231</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00380425469496132</v>
+        <v>0.00355343357833906</v>
       </c>
       <c r="F58" t="n">
-        <v>0.328923076923077</v>
+        <v>0.385230769230769</v>
       </c>
       <c r="G58" t="s">
         <v>15</v>
@@ -3158,19 +3158,19 @@
         <v>16</v>
       </c>
       <c r="I58" t="n">
-        <v>27.4250513347023</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>24.1724845995893</v>
       </c>
       <c r="K58" t="n">
-        <v>15</v>
+        <v>1423.52127078282</v>
       </c>
       <c r="L58" t="n">
-        <v>1394.62367979902</v>
+        <v>1330.82363574782</v>
       </c>
       <c r="M58" t="n">
-        <v>1432.72524617131</v>
+        <v>1368.74613714031</v>
       </c>
     </row>
     <row r="59">
@@ -3178,19 +3178,19 @@
         <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C59" t="n">
-        <v>0.114769230769231</v>
+        <v>0.0772307692307692</v>
       </c>
       <c r="D59" t="n">
-        <v>0.114769230769231</v>
+        <v>0.126</v>
       </c>
       <c r="E59" t="n">
-        <v>0.00347645271173676</v>
+        <v>0.00343554272775236</v>
       </c>
       <c r="F59" t="n">
-        <v>0.385230769230769</v>
+        <v>0.422769230769231</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
@@ -3199,19 +3199,19 @@
         <v>16</v>
       </c>
       <c r="I59" t="n">
-        <v>24.1724845995893</v>
+        <v>0.0873684210526316</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>22.9295003422313</v>
       </c>
       <c r="K59" t="n">
-        <v>37</v>
+        <v>1241.13353387424</v>
       </c>
       <c r="L59" t="n">
-        <v>1368.74613714031</v>
+        <v>1313.99836675921</v>
       </c>
       <c r="M59" t="n">
-        <v>1330.82363574782</v>
+        <v>1270.97275630001</v>
       </c>
     </row>
     <row r="60">
@@ -3219,19 +3219,19 @@
         <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0812307692307692</v>
+        <v>0.104</v>
       </c>
       <c r="D60" t="n">
-        <v>0.105423728813559</v>
+        <v>0.104</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0034240353533161</v>
+        <v>0.00336782692076057</v>
       </c>
       <c r="F60" t="n">
-        <v>0.418769230769231</v>
+        <v>0.396</v>
       </c>
       <c r="G60" t="s">
         <v>15</v>
@@ -3240,19 +3240,19 @@
         <v>16</v>
       </c>
       <c r="I60" t="n">
-        <v>27.4907597535934</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.109122807017544</v>
+        <v>20.5913757700205</v>
       </c>
       <c r="K60" t="n">
-        <v>84</v>
+        <v>1340.66635892101</v>
       </c>
       <c r="L60" t="n">
-        <v>1257.06576200764</v>
+        <v>1323.558085724</v>
       </c>
       <c r="M60" t="n">
-        <v>1372.44300068653</v>
+        <v>1210.97472684585</v>
       </c>
     </row>
     <row r="61">
@@ -3260,19 +3260,19 @@
         <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C61" t="n">
-        <v>0.124923076923077</v>
+        <v>0.0812307692307692</v>
       </c>
       <c r="D61" t="n">
-        <v>0.246190476190476</v>
+        <v>0.105423728813559</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00327185152676104</v>
+        <v>0.00327872469860892</v>
       </c>
       <c r="F61" t="n">
-        <v>0.375076923076923</v>
+        <v>0.418769230769231</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
@@ -3281,19 +3281,19 @@
         <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>31.895961670089</v>
+        <v>0.109122807017544</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0694736842105263</v>
+        <v>27.4907597535934</v>
       </c>
       <c r="K61" t="n">
-        <v>160</v>
+        <v>1307.03500357302</v>
       </c>
       <c r="L61" t="n">
-        <v>1396.73705554117</v>
+        <v>1372.44300068653</v>
       </c>
       <c r="M61" t="n">
-        <v>1392.8901065853</v>
+        <v>1257.06576200764</v>
       </c>
     </row>
     <row r="62">
@@ -3301,19 +3301,19 @@
         <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0929230769230769</v>
+        <v>0.157846153846154</v>
       </c>
       <c r="D62" t="n">
-        <v>0.104406779661017</v>
+        <v>0.157846153846154</v>
       </c>
       <c r="E62" t="n">
-        <v>0.003234206323787</v>
+        <v>0.00317905153767323</v>
       </c>
       <c r="F62" t="n">
-        <v>0.407076923076923</v>
+        <v>0.342153846153846</v>
       </c>
       <c r="G62" t="s">
         <v>15</v>
@@ -3322,19 +3322,19 @@
         <v>16</v>
       </c>
       <c r="I62" t="n">
-        <v>26.6475017111567</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0.108070175438596</v>
+        <v>26.7433264887064</v>
       </c>
       <c r="K62" t="n">
-        <v>54</v>
+        <v>1317.99439086</v>
       </c>
       <c r="L62" t="n">
-        <v>1306.24531691601</v>
+        <v>1345.9016154514</v>
       </c>
       <c r="M62" t="n">
-        <v>1350.91736681457</v>
+        <v>1406.13491185025</v>
       </c>
     </row>
     <row r="63">
@@ -3342,19 +3342,19 @@
         <v>89</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C63" t="n">
-        <v>0.115692307692308</v>
+        <v>0.142153846153846</v>
       </c>
       <c r="D63" t="n">
-        <v>0.115692307692308</v>
+        <v>0.142153846153846</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00307362104848302</v>
+        <v>0.00303037227302907</v>
       </c>
       <c r="F63" t="n">
-        <v>0.384307692307692</v>
+        <v>0.357846153846154</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
@@ -3363,39 +3363,39 @@
         <v>16</v>
       </c>
       <c r="I63" t="n">
-        <v>28.435318275154</v>
+        <v>0.127058823529412</v>
       </c>
       <c r="J63" t="n">
-        <v>0.096140350877193</v>
+        <v>25.8699520876112</v>
       </c>
       <c r="K63" t="n">
-        <v>139</v>
+        <v>1330.77715644626</v>
       </c>
       <c r="L63" t="n">
-        <v>1300.34641790998</v>
+        <v>1274.8375564043</v>
       </c>
       <c r="M63" t="n">
-        <v>1332.14989303076</v>
+        <v>1414.09617633426</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0636923076923077</v>
+        <v>0.107384615384615</v>
       </c>
       <c r="D64" t="n">
-        <v>0.133015873015873</v>
+        <v>0.107384615384615</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00298845675682787</v>
+        <v>0.00296127685792299</v>
       </c>
       <c r="F64" t="n">
-        <v>0.436307692307692</v>
+        <v>0.392615384615385</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
@@ -3404,39 +3404,39 @@
         <v>16</v>
       </c>
       <c r="I64" t="n">
-        <v>31.419575633128</v>
+        <v>0.0996491228070175</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0410526315789474</v>
+        <v>26.9568788501027</v>
       </c>
       <c r="K64" t="n">
-        <v>181</v>
+        <v>1386.57993933099</v>
       </c>
       <c r="L64" t="n">
-        <v>1281.80709561178</v>
+        <v>1330.33398602716</v>
       </c>
       <c r="M64" t="n">
-        <v>1395.03171287989</v>
+        <v>1314.04968651918</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C65" t="n">
-        <v>0.157846153846154</v>
+        <v>0.0846153846153846</v>
       </c>
       <c r="D65" t="n">
-        <v>0.157846153846154</v>
+        <v>0.198</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00293134543177775</v>
+        <v>0.00293013000516573</v>
       </c>
       <c r="F65" t="n">
-        <v>0.342153846153846</v>
+        <v>0.415384615384615</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3445,39 +3445,39 @@
         <v>16</v>
       </c>
       <c r="I65" t="n">
-        <v>26.7433264887064</v>
+        <v>0.232941176470588</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>33.9739904175222</v>
       </c>
       <c r="K65" t="n">
-        <v>54</v>
+        <v>1225.88009026306</v>
       </c>
       <c r="L65" t="n">
-        <v>1406.13491185025</v>
+        <v>1377.33444148005</v>
       </c>
       <c r="M65" t="n">
-        <v>1345.9016154514</v>
+        <v>1365.90879169601</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0526153846153846</v>
+        <v>0.124923076923077</v>
       </c>
       <c r="D66" t="n">
-        <v>0.122380952380952</v>
+        <v>0.246190476190476</v>
       </c>
       <c r="E66" t="n">
-        <v>0.00290987581792693</v>
+        <v>0.00277864573718489</v>
       </c>
       <c r="F66" t="n">
-        <v>0.447384615384615</v>
+        <v>0.375076923076923</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -3486,39 +3486,39 @@
         <v>16</v>
       </c>
       <c r="I66" t="n">
-        <v>28.6789869952088</v>
+        <v>0.0694736842105263</v>
       </c>
       <c r="J66" t="n">
-        <v>0.108421052631579</v>
+        <v>31.895961670089</v>
       </c>
       <c r="K66" t="n">
-        <v>61</v>
+        <v>1080.37269595228</v>
       </c>
       <c r="L66" t="n">
-        <v>1392.88707384781</v>
+        <v>1392.8901065853</v>
       </c>
       <c r="M66" t="n">
-        <v>1355.27921646996</v>
+        <v>1396.73705554117</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C67" t="n">
-        <v>0.142153846153846</v>
+        <v>0.0547692307692308</v>
       </c>
       <c r="D67" t="n">
-        <v>0.142153846153846</v>
+        <v>0.0547692307692308</v>
       </c>
       <c r="E67" t="n">
-        <v>0.00276591315554038</v>
+        <v>0.0025674173139128</v>
       </c>
       <c r="F67" t="n">
-        <v>0.357846153846154</v>
+        <v>0.445230769230769</v>
       </c>
       <c r="G67" t="s">
         <v>15</v>
@@ -3527,39 +3527,39 @@
         <v>16</v>
       </c>
       <c r="I67" t="n">
-        <v>25.8699520876112</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0.127058823529412</v>
+        <v>22.3819301848049</v>
       </c>
       <c r="K67" t="n">
-        <v>49</v>
+        <v>1308.64619952678</v>
       </c>
       <c r="L67" t="n">
-        <v>1414.09617633426</v>
+        <v>1263.54407969337</v>
       </c>
       <c r="M67" t="n">
-        <v>1274.8375564043</v>
+        <v>1356.42724816645</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0443076923076923</v>
+        <v>0.0233846153846154</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0443076923076923</v>
+        <v>0.0233846153846154</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00275433687760662</v>
+        <v>0.00255755438394979</v>
       </c>
       <c r="F68" t="n">
-        <v>0.455692307692308</v>
+        <v>0.476615384615385</v>
       </c>
       <c r="G68" t="s">
         <v>15</v>
@@ -3568,39 +3568,39 @@
         <v>16</v>
       </c>
       <c r="I68" t="n">
-        <v>21.305954825462</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>23.3593429158111</v>
       </c>
       <c r="K68" t="n">
-        <v>9</v>
+        <v>1249.63962474064</v>
       </c>
       <c r="L68" t="n">
-        <v>1271.72580558593</v>
+        <v>1311.81436104358</v>
       </c>
       <c r="M68" t="n">
-        <v>1273.44276960971</v>
+        <v>1263.8132653586</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C69" t="n">
-        <v>0.107384615384615</v>
+        <v>0.0443076923076923</v>
       </c>
       <c r="D69" t="n">
-        <v>0.107384615384615</v>
+        <v>0.0443076923076923</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00265257745461092</v>
+        <v>0.0025062998085711</v>
       </c>
       <c r="F69" t="n">
-        <v>0.392615384615385</v>
+        <v>0.455692307692308</v>
       </c>
       <c r="G69" t="s">
         <v>15</v>
@@ -3609,39 +3609,39 @@
         <v>16</v>
       </c>
       <c r="I69" t="n">
-        <v>26.9568788501027</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0996491228070175</v>
+        <v>21.305954825462</v>
       </c>
       <c r="K69" t="n">
-        <v>53</v>
+        <v>1267.12180093125</v>
       </c>
       <c r="L69" t="n">
-        <v>1314.04968651918</v>
+        <v>1273.44276960971</v>
       </c>
       <c r="M69" t="n">
-        <v>1330.33398602716</v>
+        <v>1271.72580558593</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0233846153846154</v>
+        <v>0.0972307692307692</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0233846153846154</v>
+        <v>0.0972307692307692</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0026217806397924</v>
+        <v>0.0024453038637718</v>
       </c>
       <c r="F70" t="n">
-        <v>0.476615384615385</v>
+        <v>0.402769230769231</v>
       </c>
       <c r="G70" t="s">
         <v>15</v>
@@ -3650,27 +3650,27 @@
         <v>16</v>
       </c>
       <c r="I70" t="n">
-        <v>23.3593429158111</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>27.378507871321</v>
       </c>
       <c r="K70" t="n">
-        <v>19</v>
+        <v>1473.99512474978</v>
       </c>
       <c r="L70" t="n">
-        <v>1263.8132653586</v>
+        <v>1283.98948951066</v>
       </c>
       <c r="M70" t="n">
-        <v>1311.81436104358</v>
+        <v>1486.7630382211</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C71" t="n">
         <v>0.173230769230769</v>
@@ -3679,7 +3679,7 @@
         <v>0.187118644067797</v>
       </c>
       <c r="E71" t="n">
-        <v>0.00257389914694498</v>
+        <v>0.00239622360781159</v>
       </c>
       <c r="F71" t="n">
         <v>0.326769230769231</v>
@@ -3691,39 +3691,39 @@
         <v>16</v>
       </c>
       <c r="I71" t="n">
+        <v>0.193684210526316</v>
+      </c>
+      <c r="J71" t="n">
         <v>32.1341546885695</v>
       </c>
-      <c r="J71" t="n">
-        <v>0.193684210526316</v>
-      </c>
       <c r="K71" t="n">
-        <v>154</v>
+        <v>1100.18110230003</v>
       </c>
       <c r="L71" t="n">
+        <v>1316.10375150417</v>
+      </c>
+      <c r="M71" t="n">
         <v>1431.66528916872</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1316.10375150417</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0547692307692308</v>
+        <v>0.0664615384615385</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0547692307692308</v>
+        <v>0.0874576271186441</v>
       </c>
       <c r="E72" t="n">
-        <v>0.00256329251530378</v>
+        <v>0.00235126635116107</v>
       </c>
       <c r="F72" t="n">
-        <v>0.445230769230769</v>
+        <v>0.433538461538462</v>
       </c>
       <c r="G72" t="s">
         <v>15</v>
@@ -3732,39 +3732,39 @@
         <v>16</v>
       </c>
       <c r="I72" t="n">
-        <v>22.3819301848049</v>
+        <v>0.0905263157894737</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>26.7624914442163</v>
       </c>
       <c r="K72" t="n">
-        <v>11</v>
+        <v>1400.30339675546</v>
       </c>
       <c r="L72" t="n">
-        <v>1356.42724816645</v>
+        <v>1306.64911929176</v>
       </c>
       <c r="M72" t="n">
-        <v>1263.54407969337</v>
+        <v>1283.23286690874</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" t="s">
         <v>100</v>
       </c>
-      <c r="B73" t="s">
-        <v>55</v>
-      </c>
       <c r="C73" t="n">
-        <v>0.0458461538461538</v>
+        <v>0.115692307692308</v>
       </c>
       <c r="D73" t="n">
-        <v>0.213898305084746</v>
+        <v>0.115692307692308</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00255641817286556</v>
+        <v>0.00234470953271127</v>
       </c>
       <c r="F73" t="n">
-        <v>0.454153846153846</v>
+        <v>0.384307692307692</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
@@ -3773,19 +3773,19 @@
         <v>16</v>
       </c>
       <c r="I73" t="n">
-        <v>35.4442162902122</v>
+        <v>0.096140350877193</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0996491228070175</v>
+        <v>28.435318275154</v>
       </c>
       <c r="K73" t="n">
-        <v>229</v>
+        <v>1197.74688931425</v>
       </c>
       <c r="L73" t="n">
-        <v>1218.85908755817</v>
+        <v>1332.14989303076</v>
       </c>
       <c r="M73" t="n">
-        <v>1435.18975329966</v>
+        <v>1300.34641790998</v>
       </c>
     </row>
     <row r="74">
@@ -3793,7 +3793,7 @@
         <v>101</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C74" t="n">
         <v>0.110461538461538</v>
@@ -3802,7 +3802,7 @@
         <v>0.110461538461538</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00231754054281032</v>
+        <v>0.0022437307168211</v>
       </c>
       <c r="F74" t="n">
         <v>0.389538461538462</v>
@@ -3814,19 +3814,19 @@
         <v>16</v>
       </c>
       <c r="I74" t="n">
+        <v>0.0698245614035088</v>
+      </c>
+      <c r="J74" t="n">
         <v>27.958932238193</v>
       </c>
-      <c r="J74" t="n">
-        <v>0.0698245614035088</v>
-      </c>
       <c r="K74" t="n">
-        <v>81</v>
+        <v>1126.41736147765</v>
       </c>
       <c r="L74" t="n">
+        <v>1317.69814422186</v>
+      </c>
+      <c r="M74" t="n">
         <v>1338.81290970126</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1317.69814422186</v>
       </c>
     </row>
     <row r="75">
@@ -3834,19 +3834,19 @@
         <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C75" t="n">
-        <v>0.110769230769231</v>
+        <v>0.0636923076923077</v>
       </c>
       <c r="D75" t="n">
-        <v>0.246190476190476</v>
+        <v>0.133015873015873</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00231320725545981</v>
+        <v>0.0021929196017823</v>
       </c>
       <c r="F75" t="n">
-        <v>0.389230769230769</v>
+        <v>0.436307692307692</v>
       </c>
       <c r="G75" t="s">
         <v>15</v>
@@ -3855,19 +3855,19 @@
         <v>16</v>
       </c>
       <c r="I75" t="n">
-        <v>33.7577002053388</v>
+        <v>0.0410526315789474</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0905263157894737</v>
+        <v>31.419575633128</v>
       </c>
       <c r="K75" t="n">
-        <v>184</v>
+        <v>1213.37213104866</v>
       </c>
       <c r="L75" t="n">
-        <v>1332.28119598812</v>
+        <v>1395.03171287989</v>
       </c>
       <c r="M75" t="n">
-        <v>1381.51269887943</v>
+        <v>1281.80709561178</v>
       </c>
     </row>
     <row r="76">
@@ -3875,19 +3875,19 @@
         <v>103</v>
       </c>
       <c r="B76" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0603076923076923</v>
+        <v>0.0963076923076923</v>
       </c>
       <c r="D76" t="n">
-        <v>0.140327868852459</v>
+        <v>0.137627118644068</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00225462356327943</v>
+        <v>0.00203634433909804</v>
       </c>
       <c r="F76" t="n">
-        <v>0.439692307692308</v>
+        <v>0.403692307692308</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
@@ -3896,39 +3896,39 @@
         <v>16</v>
       </c>
       <c r="I76" t="n">
-        <v>28.2354551676934</v>
+        <v>0.142456140350877</v>
       </c>
       <c r="J76" t="n">
-        <v>0.114736842105263</v>
+        <v>27.2826830937714</v>
       </c>
       <c r="K76" t="n">
-        <v>150</v>
+        <v>1407.86261770998</v>
       </c>
       <c r="L76" t="n">
-        <v>1272.09619533949</v>
+        <v>1228.00658738988</v>
       </c>
       <c r="M76" t="n">
-        <v>1275.20037989351</v>
+        <v>1419.24521602762</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B77" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0806153846153846</v>
+        <v>0.110769230769231</v>
       </c>
       <c r="D77" t="n">
-        <v>0.282380952380952</v>
+        <v>0.246190476190476</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00221402497113308</v>
+        <v>0.00194618280039287</v>
       </c>
       <c r="F77" t="n">
-        <v>0.419384615384615</v>
+        <v>0.389230769230769</v>
       </c>
       <c r="G77" t="s">
         <v>15</v>
@@ -3937,39 +3937,39 @@
         <v>16</v>
       </c>
       <c r="I77" t="n">
-        <v>32.0684462696783</v>
+        <v>0.0905263157894737</v>
       </c>
       <c r="J77" t="n">
-        <v>0.16</v>
+        <v>33.7577002053388</v>
       </c>
       <c r="K77" t="n">
-        <v>212</v>
+        <v>1134.15683374376</v>
       </c>
       <c r="L77" t="n">
-        <v>1397.05935600254</v>
+        <v>1381.51269887943</v>
       </c>
       <c r="M77" t="n">
-        <v>1271.65580119664</v>
+        <v>1332.28119598812</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0963076923076923</v>
+        <v>0.0529230769230769</v>
       </c>
       <c r="D78" t="n">
-        <v>0.137627118644068</v>
+        <v>0.0529230769230769</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00218668150082581</v>
+        <v>0.00191197551844747</v>
       </c>
       <c r="F78" t="n">
-        <v>0.403692307692308</v>
+        <v>0.447076923076923</v>
       </c>
       <c r="G78" t="s">
         <v>15</v>
@@ -3978,39 +3978,39 @@
         <v>16</v>
       </c>
       <c r="I78" t="n">
-        <v>27.2826830937714</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.142456140350877</v>
+        <v>24.6461327857632</v>
       </c>
       <c r="K78" t="n">
-        <v>105</v>
+        <v>1333.71992290971</v>
       </c>
       <c r="L78" t="n">
-        <v>1419.24521602762</v>
+        <v>1285.67345625525</v>
       </c>
       <c r="M78" t="n">
-        <v>1228.00658738988</v>
+        <v>1264.52953059235</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B79" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0664615384615385</v>
+        <v>0.0458461538461538</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0874576271186441</v>
+        <v>0.213898305084746</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00214627174905029</v>
+        <v>0.00188755267100265</v>
       </c>
       <c r="F79" t="n">
-        <v>0.433538461538462</v>
+        <v>0.454153846153846</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
@@ -4019,39 +4019,39 @@
         <v>16</v>
       </c>
       <c r="I79" t="n">
-        <v>26.7624914442163</v>
+        <v>0.0996491228070175</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0905263157894737</v>
+        <v>35.4442162902122</v>
       </c>
       <c r="K79" t="n">
-        <v>52</v>
+        <v>1217.17083414454</v>
       </c>
       <c r="L79" t="n">
-        <v>1283.23286690874</v>
+        <v>1435.18975329966</v>
       </c>
       <c r="M79" t="n">
-        <v>1306.64911929176</v>
+        <v>1218.85908755817</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0329230769230769</v>
+        <v>0.0636923076923077</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0742857142857143</v>
+        <v>0.0885</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00200579005293958</v>
+        <v>0.0017819515437585</v>
       </c>
       <c r="F80" t="n">
-        <v>0.467076923076923</v>
+        <v>0.436307692307692</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
@@ -4060,39 +4060,39 @@
         <v>16</v>
       </c>
       <c r="I80" t="n">
-        <v>24.5475701574264</v>
+        <v>0.0294736842105263</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0764912280701754</v>
+        <v>24.1587953456537</v>
       </c>
       <c r="K80" t="n">
-        <v>68</v>
+        <v>1296.85815093371</v>
       </c>
       <c r="L80" t="n">
-        <v>1267.96111111346</v>
+        <v>1266.9068834077</v>
       </c>
       <c r="M80" t="n">
-        <v>1239.587809522</v>
+        <v>1238.67713438405</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0636923076923077</v>
+        <v>0.0329230769230769</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0885</v>
+        <v>0.0742857142857143</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00194840265415066</v>
+        <v>0.00171806189625177</v>
       </c>
       <c r="F81" t="n">
-        <v>0.436307692307692</v>
+        <v>0.467076923076923</v>
       </c>
       <c r="G81" t="s">
         <v>15</v>
@@ -4101,39 +4101,39 @@
         <v>16</v>
       </c>
       <c r="I81" t="n">
-        <v>24.1587953456537</v>
+        <v>0.0764912280701754</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0294736842105263</v>
+        <v>24.5475701574264</v>
       </c>
       <c r="K81" t="n">
-        <v>44</v>
+        <v>1313.79526817923</v>
       </c>
       <c r="L81" t="n">
-        <v>1238.67713438405</v>
+        <v>1239.587809522</v>
       </c>
       <c r="M81" t="n">
-        <v>1266.9068834077</v>
+        <v>1267.96111111346</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0972307692307692</v>
+        <v>0.0535384615384615</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0972307692307692</v>
+        <v>0.158095238095238</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00193669882465786</v>
+        <v>0.00168929710725165</v>
       </c>
       <c r="F82" t="n">
-        <v>0.402769230769231</v>
+        <v>0.446461538461538</v>
       </c>
       <c r="G82" t="s">
         <v>15</v>
@@ -4142,27 +4142,27 @@
         <v>16</v>
       </c>
       <c r="I82" t="n">
-        <v>27.378507871321</v>
+        <v>0.0652631578947368</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>30.6255989048597</v>
       </c>
       <c r="K82" t="n">
-        <v>44</v>
+        <v>1460.36725347938</v>
       </c>
       <c r="L82" t="n">
-        <v>1486.7630382211</v>
+        <v>1280.18391446566</v>
       </c>
       <c r="M82" t="n">
-        <v>1283.98948951066</v>
+        <v>1416.91561649289</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C83" t="n">
         <v>0.0236923076923077</v>
@@ -4171,7 +4171,7 @@
         <v>0.0236923076923077</v>
       </c>
       <c r="E83" t="n">
-        <v>0.00188159757732958</v>
+        <v>0.00168285229043493</v>
       </c>
       <c r="F83" t="n">
         <v>0.476307692307692</v>
@@ -4183,39 +4183,39 @@
         <v>16</v>
       </c>
       <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
         <v>21.5989048596851</v>
       </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
       <c r="K83" t="n">
-        <v>13</v>
+        <v>1272.48973248935</v>
       </c>
       <c r="L83" t="n">
+        <v>1231.95428559327</v>
+      </c>
+      <c r="M83" t="n">
         <v>1234.10685122193</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1231.95428559327</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>112</v>
+      </c>
+      <c r="B84" t="s">
         <v>113</v>
       </c>
-      <c r="B84" t="s">
-        <v>114</v>
-      </c>
       <c r="C84" t="n">
-        <v>0.0184615384615385</v>
+        <v>0.0603076923076923</v>
       </c>
       <c r="D84" t="n">
-        <v>0.149491525423729</v>
+        <v>0.140327868852459</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00181229499021329</v>
+        <v>0.00165615521821593</v>
       </c>
       <c r="F84" t="n">
-        <v>0.481538461538462</v>
+        <v>0.439692307692308</v>
       </c>
       <c r="G84" t="s">
         <v>15</v>
@@ -4224,39 +4224,39 @@
         <v>16</v>
       </c>
       <c r="I84" t="n">
-        <v>27.2580424366872</v>
+        <v>0.114736842105263</v>
       </c>
       <c r="J84" t="n">
-        <v>0.154736842105263</v>
+        <v>28.2354551676934</v>
       </c>
       <c r="K84" t="n">
-        <v>132</v>
+        <v>1338.86056255086</v>
       </c>
       <c r="L84" t="n">
-        <v>1264.98807928171</v>
+        <v>1275.20037989351</v>
       </c>
       <c r="M84" t="n">
-        <v>1220.31669063585</v>
+        <v>1272.09619533949</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0529230769230769</v>
+        <v>0.0806153846153846</v>
       </c>
       <c r="D85" t="n">
-        <v>0.0529230769230769</v>
+        <v>0.282380952380952</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00174479000903816</v>
+        <v>0.00162288884188412</v>
       </c>
       <c r="F85" t="n">
-        <v>0.447076923076923</v>
+        <v>0.419384615384615</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
@@ -4265,27 +4265,27 @@
         <v>16</v>
       </c>
       <c r="I85" t="n">
-        <v>24.6461327857632</v>
+        <v>0.16</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>32.0684462696783</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>1372.78552350997</v>
       </c>
       <c r="L85" t="n">
-        <v>1264.52953059235</v>
+        <v>1271.65580119664</v>
       </c>
       <c r="M85" t="n">
-        <v>1285.67345625525</v>
+        <v>1397.05935600254</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C86" t="n">
         <v>0.0864615384615385</v>
@@ -4294,7 +4294,7 @@
         <v>0.171904761904762</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00158650138840834</v>
+        <v>0.00158032013615363</v>
       </c>
       <c r="F86" t="n">
         <v>0.413538461538462</v>
@@ -4306,39 +4306,39 @@
         <v>16</v>
       </c>
       <c r="I86" t="n">
+        <v>0.116842105263158</v>
+      </c>
+      <c r="J86" t="n">
         <v>30.9322381930185</v>
       </c>
-      <c r="J86" t="n">
-        <v>0.116842105263158</v>
-      </c>
       <c r="K86" t="n">
-        <v>132</v>
+        <v>1407.92052788336</v>
       </c>
       <c r="L86" t="n">
+        <v>1271.84990718483</v>
+      </c>
+      <c r="M86" t="n">
         <v>1375.97129032249</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1271.84990718483</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>116</v>
+      </c>
+      <c r="B87" t="s">
         <v>117</v>
       </c>
-      <c r="B87" t="s">
-        <v>35</v>
-      </c>
       <c r="C87" t="n">
-        <v>0.0535384615384615</v>
+        <v>0.0184615384615385</v>
       </c>
       <c r="D87" t="n">
-        <v>0.158095238095238</v>
+        <v>0.149491525423729</v>
       </c>
       <c r="E87" t="n">
-        <v>0.00139713312232402</v>
+        <v>0.00135039560995335</v>
       </c>
       <c r="F87" t="n">
-        <v>0.446461538461538</v>
+        <v>0.481538461538462</v>
       </c>
       <c r="G87" t="s">
         <v>15</v>
@@ -4347,19 +4347,19 @@
         <v>16</v>
       </c>
       <c r="I87" t="n">
-        <v>30.6255989048597</v>
+        <v>0.154736842105263</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0652631578947368</v>
+        <v>27.2580424366872</v>
       </c>
       <c r="K87" t="n">
-        <v>91</v>
+        <v>1264.16285123337</v>
       </c>
       <c r="L87" t="n">
-        <v>1416.91561649289</v>
+        <v>1220.31669063585</v>
       </c>
       <c r="M87" t="n">
-        <v>1280.18391446566</v>
+        <v>1264.98807928171</v>
       </c>
     </row>
     <row r="88">
@@ -4367,7 +4367,7 @@
         <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C88" t="n">
         <v>0.0664615384615385</v>
@@ -4376,7 +4376,7 @@
         <v>0.0664615384615385</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00122909973749366</v>
+        <v>0.00114683274362563</v>
       </c>
       <c r="F88" t="n">
         <v>0.433538461538462</v>
@@ -4388,19 +4388,19 @@
         <v>16</v>
       </c>
       <c r="I88" t="n">
+        <v>0.0596491228070175</v>
+      </c>
+      <c r="J88" t="n">
         <v>30.6009582477755</v>
       </c>
-      <c r="J88" t="n">
-        <v>0.0596491228070175</v>
-      </c>
       <c r="K88" t="n">
-        <v>119</v>
+        <v>1246.21586376132</v>
       </c>
       <c r="L88" t="n">
+        <v>1293.93989170002</v>
+      </c>
+      <c r="M88" t="n">
         <v>1237.05565348768</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1293.93989170002</v>
       </c>
     </row>
     <row r="89">
@@ -4408,19 +4408,19 @@
         <v>119</v>
       </c>
       <c r="B89" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="C89" t="n">
-        <v>0.00738461538461538</v>
+        <v>0.0190769230769231</v>
       </c>
       <c r="D89" t="n">
-        <v>0.0075</v>
+        <v>0.112881355932203</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00115014924057461</v>
+        <v>0.00112095234645846</v>
       </c>
       <c r="F89" t="n">
-        <v>0.492615384615385</v>
+        <v>0.480923076923077</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
@@ -4429,19 +4429,19 @@
         <v>16</v>
       </c>
       <c r="I89" t="n">
-        <v>22.1930184804928</v>
+        <v>0.116842105263158</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>33.4592744695414</v>
       </c>
       <c r="K89" t="n">
-        <v>16</v>
+        <v>1219.65816771157</v>
       </c>
       <c r="L89" t="n">
-        <v>1146.53835368705</v>
+        <v>1271.77447289612</v>
       </c>
       <c r="M89" t="n">
-        <v>1196.46640220873</v>
+        <v>1364.66803830286</v>
       </c>
     </row>
     <row r="90">
@@ -4449,40 +4449,40 @@
         <v>120</v>
       </c>
       <c r="B90" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="C90" t="n">
+        <v>0.00707692307692308</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.00707692307692308</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.000994856428212806</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.492923076923077</v>
+      </c>
+      <c r="G90" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" t="n">
         <v>0</v>
       </c>
-      <c r="D90" t="n">
-        <v>0.0647457627118644</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0.00100863239195702</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G90" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" t="s">
-        <v>16</v>
-      </c>
-      <c r="I90" t="n">
-        <v>24.9390828199863</v>
-      </c>
       <c r="J90" t="n">
-        <v>0.0670175438596491</v>
+        <v>25.5277207392197</v>
       </c>
       <c r="K90" t="n">
-        <v>50</v>
+        <v>1289.48481198342</v>
       </c>
       <c r="L90" t="n">
-        <v>1216.97688731791</v>
+        <v>1206.02256186022</v>
       </c>
       <c r="M90" t="n">
-        <v>1177.82312327424</v>
+        <v>1261.74644757135</v>
       </c>
     </row>
     <row r="91">
@@ -4490,19 +4490,19 @@
         <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="C91" t="n">
-        <v>0.00676923076923077</v>
+        <v>0.00738461538461538</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00676923076923077</v>
+        <v>0.0075</v>
       </c>
       <c r="E91" t="n">
-        <v>0.000932003351180068</v>
+        <v>0.000991702705912185</v>
       </c>
       <c r="F91" t="n">
-        <v>0.493230769230769</v>
+        <v>0.492615384615385</v>
       </c>
       <c r="G91" t="s">
         <v>15</v>
@@ -4511,19 +4511,19 @@
         <v>16</v>
       </c>
       <c r="I91" t="n">
-        <v>24.580424366872</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>22.1930184804928</v>
       </c>
       <c r="K91" t="n">
-        <v>13</v>
+        <v>1184.66665875218</v>
       </c>
       <c r="L91" t="n">
-        <v>1226.86348909833</v>
+        <v>1196.46640220873</v>
       </c>
       <c r="M91" t="n">
-        <v>1203.19290498576</v>
+        <v>1146.53835368705</v>
       </c>
     </row>
     <row r="92">
@@ -4531,19 +4531,19 @@
         <v>122</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.00676923076923077</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.00676923076923077</v>
       </c>
       <c r="E92" t="n">
-        <v>0.000903388350056381</v>
+        <v>0.000986770645209324</v>
       </c>
       <c r="F92" t="n">
-        <v>0.486461538461538</v>
+        <v>0.493230769230769</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
@@ -4552,39 +4552,39 @@
         <v>16</v>
       </c>
       <c r="I92" t="n">
-        <v>24.0438056125941</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>24.580424366872</v>
       </c>
       <c r="K92" t="n">
-        <v>13</v>
+        <v>1253.85034268986</v>
       </c>
       <c r="L92" t="n">
-        <v>1206.0825484611</v>
+        <v>1203.19290498576</v>
       </c>
       <c r="M92" t="n">
-        <v>1191.30147133873</v>
+        <v>1226.86348909833</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B93" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="C93" t="n">
-        <v>0.00707692307692308</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00707692307692308</v>
+        <v>0.0647457627118644</v>
       </c>
       <c r="E93" t="n">
-        <v>0.000864106508869271</v>
+        <v>0.000931714196081385</v>
       </c>
       <c r="F93" t="n">
-        <v>0.492923076923077</v>
+        <v>0.5</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
@@ -4593,39 +4593,39 @@
         <v>16</v>
       </c>
       <c r="I93" t="n">
-        <v>25.5277207392197</v>
+        <v>0.0670175438596491</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>24.9390828199863</v>
       </c>
       <c r="K93" t="n">
-        <v>12</v>
+        <v>1279.78803514376</v>
       </c>
       <c r="L93" t="n">
-        <v>1261.74644757135</v>
+        <v>1177.82312327424</v>
       </c>
       <c r="M93" t="n">
-        <v>1206.02256186022</v>
+        <v>1216.97688731791</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" t="s">
         <v>125</v>
       </c>
-      <c r="B94" t="s">
-        <v>35</v>
-      </c>
       <c r="C94" t="n">
-        <v>0.0190769230769231</v>
+        <v>0.0135384615384615</v>
       </c>
       <c r="D94" t="n">
-        <v>0.112881355932203</v>
+        <v>0.0135384615384615</v>
       </c>
       <c r="E94" t="n">
-        <v>0.000836784799901866</v>
+        <v>0.000908419379773931</v>
       </c>
       <c r="F94" t="n">
-        <v>0.480923076923077</v>
+        <v>0.486461538461538</v>
       </c>
       <c r="G94" t="s">
         <v>15</v>
@@ -4634,19 +4634,19 @@
         <v>16</v>
       </c>
       <c r="I94" t="n">
-        <v>33.4592744695414</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0.116842105263158</v>
+        <v>24.0438056125941</v>
       </c>
       <c r="K94" t="n">
-        <v>91</v>
+        <v>1211.44098510954</v>
       </c>
       <c r="L94" t="n">
-        <v>1364.66803830286</v>
+        <v>1191.30147133873</v>
       </c>
       <c r="M94" t="n">
-        <v>1271.77447289612</v>
+        <v>1206.0825484611</v>
       </c>
     </row>
     <row r="95">
@@ -4654,19 +4654,19 @@
         <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="C95" t="n">
-        <v>0.044</v>
+        <v>0.0206153846153846</v>
       </c>
       <c r="D95" t="n">
-        <v>0.160727272727273</v>
+        <v>0.0933333333333333</v>
       </c>
       <c r="E95" t="n">
-        <v>0.000800645198990603</v>
+        <v>0.000884388120929784</v>
       </c>
       <c r="F95" t="n">
-        <v>0.456</v>
+        <v>0.479384615384615</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
@@ -4675,19 +4675,19 @@
         <v>16</v>
       </c>
       <c r="I95" t="n">
-        <v>34.1245722108145</v>
+        <v>0.0947368421052632</v>
       </c>
       <c r="J95" t="n">
-        <v>0.165614035087719</v>
+        <v>31.5373032169747</v>
       </c>
       <c r="K95" t="n">
-        <v>245</v>
+        <v>1335.09614869109</v>
       </c>
       <c r="L95" t="n">
-        <v>1271.44799007319</v>
+        <v>1224.1198382179</v>
       </c>
       <c r="M95" t="n">
-        <v>1181.81251826923</v>
+        <v>1325.25478480542</v>
       </c>
     </row>
     <row r="96">
@@ -4695,19 +4695,19 @@
         <v>127</v>
       </c>
       <c r="B96" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0421538461538462</v>
+        <v>0.0446153846153846</v>
       </c>
       <c r="D96" t="n">
-        <v>0.07</v>
+        <v>0.0715254237288136</v>
       </c>
       <c r="E96" t="n">
-        <v>0.000798312949029848</v>
+        <v>0.000748222683901514</v>
       </c>
       <c r="F96" t="n">
-        <v>0.457846153846154</v>
+        <v>0.455384615384615</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
@@ -4716,19 +4716,19 @@
         <v>16</v>
       </c>
       <c r="I96" t="n">
-        <v>28.6461327857632</v>
+        <v>0.0740350877192982</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0487719298245614</v>
+        <v>30.4640657084189</v>
       </c>
       <c r="K96" t="n">
-        <v>108</v>
+        <v>1188.27448494651</v>
       </c>
       <c r="L96" t="n">
-        <v>1214.93236428129</v>
+        <v>1220.41256111428</v>
       </c>
       <c r="M96" t="n">
-        <v>1199.55771996603</v>
+        <v>1253.29808146112</v>
       </c>
     </row>
     <row r="97">
@@ -4736,19 +4736,19 @@
         <v>128</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0206153846153846</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.0933333333333333</v>
+        <v>0.0176271186440678</v>
       </c>
       <c r="E97" t="n">
-        <v>0.000795677713812875</v>
+        <v>0.00072095351414243</v>
       </c>
       <c r="F97" t="n">
-        <v>0.479384615384615</v>
+        <v>0.5</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
@@ -4757,19 +4757,19 @@
         <v>16</v>
       </c>
       <c r="I97" t="n">
-        <v>31.5373032169747</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0947368421052632</v>
+        <v>25.3607118412047</v>
       </c>
       <c r="K97" t="n">
-        <v>107</v>
+        <v>1248.46162065852</v>
       </c>
       <c r="L97" t="n">
-        <v>1325.25478480542</v>
+        <v>1184.68668384022</v>
       </c>
       <c r="M97" t="n">
-        <v>1224.1198382179</v>
+        <v>1181.89115983615</v>
       </c>
     </row>
     <row r="98">
@@ -4777,19 +4777,19 @@
         <v>129</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0446153846153846</v>
+        <v>0.0421538461538462</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0715254237288136</v>
+        <v>0.07</v>
       </c>
       <c r="E98" t="n">
-        <v>0.000723607321511953</v>
+        <v>0.000695155164186774</v>
       </c>
       <c r="F98" t="n">
-        <v>0.455384615384615</v>
+        <v>0.457846153846154</v>
       </c>
       <c r="G98" t="s">
         <v>15</v>
@@ -4798,19 +4798,19 @@
         <v>16</v>
       </c>
       <c r="I98" t="n">
-        <v>30.4640657084189</v>
+        <v>0.0487719298245614</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0740350877192982</v>
+        <v>28.6461327857632</v>
       </c>
       <c r="K98" t="n">
-        <v>94</v>
+        <v>1294.88569704496</v>
       </c>
       <c r="L98" t="n">
-        <v>1253.29808146112</v>
+        <v>1199.55771996603</v>
       </c>
       <c r="M98" t="n">
-        <v>1220.41256111428</v>
+        <v>1214.93236428129</v>
       </c>
     </row>
     <row r="99">
@@ -4818,40 +4818,40 @@
         <v>130</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C99" t="n">
+        <v>0.0135384615384615</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.0135384615384615</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.000619888131149434</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.486461538461538</v>
+      </c>
+      <c r="G99" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" t="n">
         <v>0</v>
       </c>
-      <c r="D99" t="n">
-        <v>0.0176271186440678</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0.000672239783545553</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G99" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" t="s">
-        <v>16</v>
-      </c>
-      <c r="I99" t="n">
-        <v>25.3607118412047</v>
-      </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>27.170431211499</v>
       </c>
       <c r="K99" t="n">
-        <v>16</v>
+        <v>1185.72298502975</v>
       </c>
       <c r="L99" t="n">
-        <v>1181.89115983615</v>
+        <v>1180.74280819761</v>
       </c>
       <c r="M99" t="n">
-        <v>1184.68668384022</v>
+        <v>1218.48717749614</v>
       </c>
     </row>
     <row r="100">
@@ -4859,7 +4859,7 @@
         <v>131</v>
       </c>
       <c r="B100" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C100" t="n">
         <v>0.0289230769230769</v>
@@ -4868,7 +4868,7 @@
         <v>0.0289230769230769</v>
       </c>
       <c r="E100" t="n">
-        <v>0.000575164460213312</v>
+        <v>0.000606085342392592</v>
       </c>
       <c r="F100" t="n">
         <v>0.471076923076923</v>
@@ -4880,19 +4880,19 @@
         <v>16</v>
       </c>
       <c r="I100" t="n">
+        <v>0.0114285714285714</v>
+      </c>
+      <c r="J100" t="n">
         <v>28.2737850787132</v>
       </c>
-      <c r="J100" t="n">
-        <v>0.0114285714285714</v>
-      </c>
       <c r="K100" t="n">
-        <v>53</v>
+        <v>1233.51169403177</v>
       </c>
       <c r="L100" t="n">
+        <v>1214.35534681034</v>
+      </c>
+      <c r="M100" t="n">
         <v>1142.38883668489</v>
-      </c>
-      <c r="M100" t="n">
-        <v>1214.35534681034</v>
       </c>
     </row>
     <row r="101">
@@ -4900,19 +4900,19 @@
         <v>132</v>
       </c>
       <c r="B101" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.044</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.160727272727273</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000559273424814354</v>
+        <v>0.000534221939455651</v>
       </c>
       <c r="F101" t="n">
-        <v>0.486461538461538</v>
+        <v>0.456</v>
       </c>
       <c r="G101" t="s">
         <v>15</v>
@@ -4921,19 +4921,19 @@
         <v>16</v>
       </c>
       <c r="I101" t="n">
-        <v>27.170431211499</v>
+        <v>0.165614035087719</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>34.1245722108145</v>
       </c>
       <c r="K101" t="n">
-        <v>31</v>
+        <v>1349.0390402962</v>
       </c>
       <c r="L101" t="n">
-        <v>1218.48717749614</v>
+        <v>1181.81251826923</v>
       </c>
       <c r="M101" t="n">
-        <v>1180.74280819761</v>
+        <v>1271.44799007319</v>
       </c>
     </row>
     <row r="102">
@@ -4950,7 +4950,7 @@
         <v>0.039047619047619</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000484605094509162</v>
+        <v>0.000409939337538844</v>
       </c>
       <c r="F102" t="n">
         <v>0.5</v>
@@ -4962,19 +4962,19 @@
         <v>16</v>
       </c>
       <c r="I102" t="n">
+        <v>0.0455555555555556</v>
+      </c>
+      <c r="J102" t="n">
         <v>25.596167008898</v>
       </c>
-      <c r="J102" t="n">
-        <v>0.0455555555555556</v>
-      </c>
       <c r="K102" t="n">
-        <v>54</v>
+        <v>1121.60891494279</v>
       </c>
       <c r="L102" t="n">
+        <v>1134.27003101503</v>
+      </c>
+      <c r="M102" t="n">
         <v>1060.92117843046</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1134.27003101503</v>
       </c>
     </row>
     <row r="103">
@@ -4982,19 +4982,19 @@
         <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0270769230769231</v>
+        <v>0.0212307692307692</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0374603174603175</v>
+        <v>0.0526984126984127</v>
       </c>
       <c r="E103" t="n">
-        <v>0.000411910246974619</v>
+        <v>0.000389867445389614</v>
       </c>
       <c r="F103" t="n">
-        <v>0.472923076923077</v>
+        <v>0.478769230769231</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
@@ -5003,39 +5003,39 @@
         <v>16</v>
       </c>
       <c r="I103" t="n">
-        <v>27.5455167693361</v>
+        <v>0.0171929824561404</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>33.2950034223135</v>
       </c>
       <c r="K103" t="n">
-        <v>83</v>
+        <v>1116.9131099004</v>
       </c>
       <c r="L103" t="n">
-        <v>1143.48493964278</v>
+        <v>1200.46486140405</v>
       </c>
       <c r="M103" t="n">
-        <v>1128.86958616484</v>
+        <v>1230.29340322432</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B104" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0212307692307692</v>
+        <v>0.02</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0526984126984127</v>
+        <v>0.0263492063492063</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000405793517588701</v>
+        <v>0.000383672183533412</v>
       </c>
       <c r="F104" t="n">
-        <v>0.478769230769231</v>
+        <v>0.48</v>
       </c>
       <c r="G104" t="s">
         <v>15</v>
@@ -5044,19 +5044,19 @@
         <v>16</v>
       </c>
       <c r="I104" t="n">
-        <v>33.2950034223135</v>
+        <v>0.00315789473684211</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0171929824561404</v>
+        <v>28.4626967830253</v>
       </c>
       <c r="K104" t="n">
-        <v>135</v>
+        <v>1180.05925954922</v>
       </c>
       <c r="L104" t="n">
-        <v>1230.29340322432</v>
+        <v>1146.19712818139</v>
       </c>
       <c r="M104" t="n">
-        <v>1200.46486140405</v>
+        <v>1169.14919463349</v>
       </c>
     </row>
     <row r="105">
@@ -5064,19 +5064,19 @@
         <v>138</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="C105" t="n">
-        <v>0.02</v>
+        <v>0.000307692307692308</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0263492063492063</v>
+        <v>0.000307692307692308</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000365718792282434</v>
+        <v>0.000353550935085419</v>
       </c>
       <c r="F105" t="n">
-        <v>0.48</v>
+        <v>0.499692307692308</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
@@ -5085,39 +5085,39 @@
         <v>16</v>
       </c>
       <c r="I105" t="n">
-        <v>28.4626967830253</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0.00315789473684211</v>
+        <v>29.2402464065708</v>
       </c>
       <c r="K105" t="n">
-        <v>54</v>
+        <v>1174.96086217118</v>
       </c>
       <c r="L105" t="n">
-        <v>1169.14919463349</v>
+        <v>1160.93598102148</v>
       </c>
       <c r="M105" t="n">
-        <v>1146.19712818139</v>
+        <v>1130.02338324035</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C106" t="n">
-        <v>0.000307692307692308</v>
+        <v>0.0270769230769231</v>
       </c>
       <c r="D106" t="n">
-        <v>0.000307692307692308</v>
+        <v>0.0374603174603175</v>
       </c>
       <c r="E106" t="n">
-        <v>0.000286831935094224</v>
+        <v>0.000353038962396952</v>
       </c>
       <c r="F106" t="n">
-        <v>0.499692307692308</v>
+        <v>0.472923076923077</v>
       </c>
       <c r="G106" t="s">
         <v>15</v>
@@ -5126,19 +5126,19 @@
         <v>16</v>
       </c>
       <c r="I106" t="n">
-        <v>29.2402464065708</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>27.5455167693361</v>
       </c>
       <c r="K106" t="n">
-        <v>27</v>
+        <v>1197.23394618571</v>
       </c>
       <c r="L106" t="n">
-        <v>1130.02338324035</v>
+        <v>1128.86958616484</v>
       </c>
       <c r="M106" t="n">
-        <v>1160.93598102148</v>
+        <v>1143.48493964278</v>
       </c>
     </row>
     <row r="107">
@@ -5146,19 +5146,19 @@
         <v>141</v>
       </c>
       <c r="B107" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0206153846153846</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0.024</v>
+        <v>0.0548275862068966</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000232793713058838</v>
+        <v>0.000284827584210144</v>
       </c>
       <c r="F107" t="n">
-        <v>0.479384615384615</v>
+        <v>0.5</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
@@ -5167,19 +5167,19 @@
         <v>16</v>
       </c>
       <c r="I107" t="n">
-        <v>27.4168377823409</v>
+        <v>0.0548275862068966</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>30.4640657084189</v>
       </c>
       <c r="K107" t="n">
-        <v>40</v>
+        <v>1212.81525680735</v>
       </c>
       <c r="L107" t="n">
-        <v>1089.28138488946</v>
+        <v>1114.80622485442</v>
       </c>
       <c r="M107" t="n">
-        <v>1087.41393336823</v>
+        <v>1164.57499958421</v>
       </c>
     </row>
     <row r="108">
@@ -5187,40 +5187,40 @@
         <v>142</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="C108" t="n">
+        <v>0.0206153846153846</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.000233982990285736</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.479384615384615</v>
+      </c>
+      <c r="G108" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" t="n">
         <v>0</v>
       </c>
-      <c r="D108" t="n">
-        <v>0.0548275862068966</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0.000218606716115932</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G108" t="s">
-        <v>15</v>
-      </c>
-      <c r="H108" t="s">
-        <v>16</v>
-      </c>
-      <c r="I108" t="n">
-        <v>30.4640657084189</v>
-      </c>
       <c r="J108" t="n">
-        <v>0.0548275862068966</v>
+        <v>27.4168377823409</v>
       </c>
       <c r="K108" t="n">
-        <v>38</v>
+        <v>1128.51836182568</v>
       </c>
       <c r="L108" t="n">
-        <v>1164.57499958421</v>
+        <v>1087.41393336823</v>
       </c>
       <c r="M108" t="n">
-        <v>1114.80622485442</v>
+        <v>1089.28138488946</v>
       </c>
     </row>
   </sheetData>
@@ -5259,19 +5259,19 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
+        <v>0.117778644977419</v>
+      </c>
+      <c r="C2" t="n">
         <v>27.1556161123798</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.117778644977419</v>
-      </c>
       <c r="D2" t="n">
-        <v>83.7476635514019</v>
+        <v>1355.12332026162</v>
       </c>
       <c r="E2" t="n">
+        <v>1356.21776199965</v>
+      </c>
+      <c r="F2" t="n">
         <v>1369.4997256828</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1356.21776199965</v>
       </c>
     </row>
   </sheetData>
@@ -5298,7 +5298,7 @@
         <v>150</v>
       </c>
       <c r="B2" t="n">
-        <v>0.91387795992714</v>
+        <v>0.918100182149363</v>
       </c>
     </row>
   </sheetData>

--- a/public/post/drafts/season-prediction/men_breakthrough-predictions-2025-final.xlsx
+++ b/public/post/drafts/season-prediction/men_breakthrough-predictions-2025-final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -40,424 +40,412 @@
     <t xml:space="preserve">Model_Confidence</t>
   </si>
   <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prev_Pct_of_Max_Points</t>
   </si>
   <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_F</t>
+    <t xml:space="preserve">Exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michal Novak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edvin Anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simen Hegstad Krüger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Jouve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Ogden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Musgrave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Britain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Didrik Tønseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Poromaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedrich Moch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Chanavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine Cyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Lapalus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Chappaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaud Jay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonas Baumann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu Hyvärinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ristomatti Hakola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valerio Grond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Even Northug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominik Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niilo Moilanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oskar Svensson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gus Schumacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maciej Starega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davide Graz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
   </si>
   <si>
     <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
   </si>
   <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Very Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Poromaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Ogden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Even Northug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simen Hegstad Krüger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Didrik Tønseth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedrich Moch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antoine Cyr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michal Novak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valerio Grond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Jouve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Lapalus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Chappaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu Hyvärinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Chanavat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gus Schumacher</t>
+    <t xml:space="preserve">Beda Klee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyril Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janik Riebli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Simenc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Clugnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Patterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janosch Brugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jens Burman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Leveille</t>
   </si>
   <si>
     <t xml:space="preserve">Lauri Vuorinen</t>
   </si>
   <si>
-    <t xml:space="preserve">Jens Burman</t>
+    <t xml:space="preserve">Remi Lindholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Häggström</t>
   </si>
   <si>
     <t xml:space="preserve">James Clinton Schoonmaker</t>
   </si>
   <si>
+    <t xml:space="preserve">Joni Mäki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markus Vuorela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Schely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naoto Baba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marcus Grate</t>
   </si>
   <si>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustaf Berglund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Lepistö</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier McKeever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin Bolger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benjamin Moser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dietmar Nöckler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vili Crv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Föttinger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giandomenico Salvadori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bögl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Jager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian Notz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paolo Ventura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludek Seller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seve De Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sasha Masson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zanden McMullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Earnhart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamil Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anze Gros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Thomas Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattis Stenshagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Bourdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnny Hagenbuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erwan Käser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Fellner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matz William Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anian Sossau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Hirose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansgar Evensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leo Johansson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman Schaad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olzhas Klimin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nikita Gridin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candide Pralong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre Grall-Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leo Grandbois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Dapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fedor Karpov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Wolter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konstantin Bortsov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Hellweger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vladislav Kovalyov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imanol Rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julien Locke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henrik Dønnestad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Håvard Solås Taugbøl</t>
   </si>
   <si>
-    <t xml:space="preserve">Mika Vermeulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joni Mäki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattis Stenshagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niilo Moilanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo Schely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Thomas Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ristomatti Hakola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beda Klee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Lapierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davide Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyril Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaud Jay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Lindholm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Musgrave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Great Britain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Svensson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markus Vuorela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zanden McMullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leo Johansson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janik Riebli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henrik Dønnestad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matz William Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ansgar Evensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janosch Brugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Bourdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naoto Baba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludek Seller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Moser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anian Sossau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier McKeever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Lepistö</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simone Dapra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustaf Berglund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Ketterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonas Baumann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florian Notz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johnny Hagenbuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryo Hirose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sasha Masson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Hellweger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Patterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Föttinger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paolo Ventura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Giandomenico Salvadori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Clugnet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bögl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pierre Grall-Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dietmar Nöckler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Jager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Himma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roman Schaad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Earnhart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Simenc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin Bolger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominik Bury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Fellner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candide Pralong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Wolter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anze Gros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leo Grandbois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vili Crv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nikita Gridin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erwan Käser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Johannes Alev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fedor Karpov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamil Bury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konstantin Bortsov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maciej Starega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seve De Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imanol Rojo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simeon Deyanov</t>
   </si>
   <si>
     <t xml:space="preserve">Bulgaria</t>
   </si>
   <si>
-    <t xml:space="preserve">Olzhas Klimin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julien Locke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vladislav Kovalyov</t>
+    <t xml:space="preserve">Age_mean</t>
   </si>
   <si>
     <t xml:space="preserve">Prev_Pct_of_Max_Points_mean</t>
   </si>
   <si>
-    <t xml:space="preserve">Age_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_Sprint_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_C_mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prev_F_mean</t>
+    <t xml:space="preserve">Exp_mean</t>
   </si>
   <si>
     <t xml:space="preserve">Predictors_Used</t>
@@ -466,7 +454,7 @@
     <t xml:space="preserve">Model_ROC</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Pct_of_Max_Points, Age, Prev_Sprint, Prev_C, Prev_F</t>
+    <t xml:space="preserve">Age, Prev_Pct_of_Max_Points, Exp</t>
   </si>
 </sst>
 </file>
@@ -829,216 +817,180 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.458769230769231</v>
+        <v>0.201846153846154</v>
       </c>
       <c r="D2" t="n">
-        <v>0.458769230769231</v>
+        <v>0.375254237288136</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0610950460892711</v>
+        <v>0.0568855692913408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0412307692307692</v>
+        <v>0.298153846153846</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.272982456140351</v>
+        <v>27.3894592744695</v>
       </c>
       <c r="J2" t="n">
-        <v>31.958932238193</v>
+        <v>0.388421052631579</v>
       </c>
       <c r="K2" t="n">
-        <v>1379.07199098257</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1706.83124302639</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1581.73500270191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>0.314461538461538</v>
+        <v>0.328307692307692</v>
       </c>
       <c r="D3" t="n">
-        <v>0.314461538461538</v>
+        <v>0.366440677966102</v>
       </c>
       <c r="E3" t="n">
-        <v>0.049768435335312</v>
+        <v>0.0485332182516463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.185538461538462</v>
+        <v>0.171692307692308</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>0.322456140350877</v>
+        <v>21.9383983572895</v>
       </c>
       <c r="J3" t="n">
-        <v>23.2306639288159</v>
+        <v>0.379298245614035</v>
       </c>
       <c r="K3" t="n">
-        <v>1317.52297936676</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1541.94472735067</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1524.82361908068</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.241846153846154</v>
+        <v>0.313230769230769</v>
       </c>
       <c r="D4" t="n">
-        <v>0.365084745762712</v>
+        <v>0.498095238095238</v>
       </c>
       <c r="E4" t="n">
-        <v>0.049080761531926</v>
+        <v>0.0483965758712273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.258153846153846</v>
+        <v>0.186769230769231</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.377894736842105</v>
+        <v>30.9924709103354</v>
       </c>
       <c r="J4" t="n">
-        <v>23.9917864476386</v>
+        <v>0.459649122807018</v>
       </c>
       <c r="K4" t="n">
-        <v>1657.30372953512</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1536.84453870404</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1469.7451665932</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>0.264307692307692</v>
+        <v>0.292923076923077</v>
       </c>
       <c r="D5" t="n">
-        <v>0.292881355932203</v>
+        <v>0.4515</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0485495648986301</v>
+        <v>0.0483453818448796</v>
       </c>
       <c r="F5" t="n">
-        <v>0.235692307692308</v>
+        <v>0.207076923076923</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>0.303157894736842</v>
+        <v>29.3935660506502</v>
       </c>
       <c r="J5" t="n">
-        <v>28.4681724845996</v>
+        <v>0.414035087719298</v>
       </c>
       <c r="K5" t="n">
-        <v>1736.84978990624</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1594.38342349577</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1574.35570090401</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" t="n">
-        <v>0.313230769230769</v>
+        <v>0.241846153846154</v>
       </c>
       <c r="D6" t="n">
-        <v>0.498095238095238</v>
+        <v>0.365084745762712</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0483450024237103</v>
+        <v>0.0419855106433557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.186769230769231</v>
+        <v>0.258153846153846</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.459649122807018</v>
+        <v>23.9917864476386</v>
       </c>
       <c r="J6" t="n">
-        <v>30.9924709103354</v>
+        <v>0.377894736842105</v>
       </c>
       <c r="K6" t="n">
-        <v>1414.25171716748</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1557.96605530036</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1660.82001426084</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1046,122 +998,104 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>0.268615384615385</v>
+        <v>0.260307692307692</v>
       </c>
       <c r="D7" t="n">
-        <v>0.443606557377049</v>
+        <v>0.299322033898305</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0436113551064163</v>
+        <v>0.0405653376197574</v>
       </c>
       <c r="F7" t="n">
-        <v>0.231384615384615</v>
+        <v>0.239692307692308</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>0.438947368421053</v>
+        <v>34.031485284052</v>
       </c>
       <c r="J7" t="n">
-        <v>32.8514715947981</v>
+        <v>0.309824561403509</v>
       </c>
       <c r="K7" t="n">
-        <v>1334.39641407185</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1618.90213645252</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1551.32818047534</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>0.328307692307692</v>
+        <v>0.268615384615385</v>
       </c>
       <c r="D8" t="n">
-        <v>0.366440677966102</v>
+        <v>0.443606557377049</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0405924287132591</v>
+        <v>0.0394735306306837</v>
       </c>
       <c r="F8" t="n">
-        <v>0.171692307692308</v>
+        <v>0.231384615384615</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.379298245614035</v>
+        <v>32.8514715947981</v>
       </c>
       <c r="J8" t="n">
-        <v>21.9383983572895</v>
+        <v>0.438947368421053</v>
       </c>
       <c r="K8" t="n">
-        <v>1647.18255489636</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1449.49034615022</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1546.53183415041</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>0.430153846153846</v>
+        <v>0.314461538461538</v>
       </c>
       <c r="D9" t="n">
-        <v>0.430153846153846</v>
+        <v>0.314461538461538</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0366340738309437</v>
+        <v>0.0345598715027155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0698461538461538</v>
+        <v>0.185538461538462</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.298947368421053</v>
+        <v>23.2306639288159</v>
       </c>
       <c r="J9" t="n">
-        <v>23.9288158795346</v>
+        <v>0.322456140350877</v>
       </c>
       <c r="K9" t="n">
-        <v>1237.06064018222</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1533.32876556295</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1478.44852737517</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -1172,37 +1106,31 @@
         <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>0.394461538461538</v>
+        <v>0.430153846153846</v>
       </c>
       <c r="D10" t="n">
-        <v>0.394461538461538</v>
+        <v>0.430153846153846</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0287078699247201</v>
+        <v>0.0265507374311425</v>
       </c>
       <c r="F10" t="n">
-        <v>0.105538461538462</v>
+        <v>0.0698461538461538</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.263859649122807</v>
+        <v>23.9288158795346</v>
       </c>
       <c r="J10" t="n">
-        <v>25.4948665297741</v>
+        <v>0.298947368421053</v>
       </c>
       <c r="K10" t="n">
-        <v>1504.13671717247</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1530.19865287729</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1459.23100201067</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -1210,491 +1138,419 @@
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>0.201846153846154</v>
+        <v>0.259692307692308</v>
       </c>
       <c r="D11" t="n">
-        <v>0.375254237288136</v>
+        <v>0.332</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0280472935558346</v>
+        <v>0.0207169070364495</v>
       </c>
       <c r="F11" t="n">
-        <v>0.298153846153846</v>
+        <v>0.240307692307692</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.388421052631579</v>
+        <v>29.242984257358</v>
       </c>
       <c r="J11" t="n">
-        <v>27.3894592744695</v>
+        <v>0.32280701754386</v>
       </c>
       <c r="K11" t="n">
-        <v>1514.23022738537</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1482.59610165319</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1539.02370656006</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" t="n">
-        <v>0.256923076923077</v>
+        <v>0.394461538461538</v>
       </c>
       <c r="D12" t="n">
-        <v>0.256923076923077</v>
+        <v>0.394461538461538</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0245174568637964</v>
+        <v>0.0189966698140368</v>
       </c>
       <c r="F12" t="n">
-        <v>0.243076923076923</v>
+        <v>0.105538461538462</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>0.200350877192982</v>
+        <v>25.4948665297741</v>
       </c>
       <c r="J12" t="n">
-        <v>23.3839835728953</v>
+        <v>0.263859649122807</v>
       </c>
       <c r="K12" t="n">
-        <v>1662.01972011395</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1453.38593690049</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1570.56362801484</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>0.292923076923077</v>
+        <v>0.382153846153846</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4515</v>
+        <v>0.382153846153846</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0237020200181272</v>
+        <v>0.0187476340513744</v>
       </c>
       <c r="F13" t="n">
-        <v>0.207076923076923</v>
+        <v>0.117846153846154</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.414035087719298</v>
+        <v>25.6892539356605</v>
       </c>
       <c r="J13" t="n">
-        <v>29.3935660506502</v>
+        <v>0.26280701754386</v>
       </c>
       <c r="K13" t="n">
-        <v>1625.26990086273</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1475.0156284952</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1538.36106658076</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>0.382153846153846</v>
+        <v>0.273230769230769</v>
       </c>
       <c r="D14" t="n">
-        <v>0.382153846153846</v>
+        <v>0.273230769230769</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0208225701409939</v>
+        <v>0.0181992474299865</v>
       </c>
       <c r="F14" t="n">
-        <v>0.117846153846154</v>
+        <v>0.226769230769231</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.26280701754386</v>
+        <v>24.8213552361396</v>
       </c>
       <c r="J14" t="n">
-        <v>25.6892539356605</v>
+        <v>0.278947368421053</v>
       </c>
       <c r="K14" t="n">
-        <v>1180.28259287132</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1486.59649552026</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1491.6648444076</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>0.273230769230769</v>
+        <v>0.151076923076923</v>
       </c>
       <c r="D15" t="n">
-        <v>0.273230769230769</v>
+        <v>0.319661016949153</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0190874728052615</v>
+        <v>0.0168937194130392</v>
       </c>
       <c r="F15" t="n">
-        <v>0.226769230769231</v>
+        <v>0.348923076923077</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.278947368421053</v>
+        <v>32.5913757700205</v>
       </c>
       <c r="J15" t="n">
-        <v>24.8213552361396</v>
+        <v>0.330877192982456</v>
       </c>
       <c r="K15" t="n">
-        <v>1537.63177300895</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1439.67316612083</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1494.04324410132</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>0.228</v>
+        <v>0.0846153846153846</v>
       </c>
       <c r="D16" t="n">
-        <v>0.271186440677966</v>
+        <v>0.198</v>
       </c>
       <c r="E16" t="n">
-        <v>0.017633093792141</v>
+        <v>0.013939516692869</v>
       </c>
       <c r="F16" t="n">
-        <v>0.272</v>
+        <v>0.415384615384615</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>0.280701754385965</v>
+        <v>33.9739904175222</v>
       </c>
       <c r="J16" t="n">
-        <v>32.7830253251198</v>
+        <v>0.232941176470588</v>
       </c>
       <c r="K16" t="n">
-        <v>1352.37217693764</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1570.06715049991</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1459.77099509582</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C17" t="n">
-        <v>0.259692307692308</v>
+        <v>0.228</v>
       </c>
       <c r="D17" t="n">
-        <v>0.332</v>
+        <v>0.271186440677966</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0172431298199946</v>
+        <v>0.0119561951643664</v>
       </c>
       <c r="F17" t="n">
-        <v>0.240307692307692</v>
+        <v>0.272</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I17" t="n">
-        <v>0.32280701754386</v>
+        <v>32.7830253251198</v>
       </c>
       <c r="J17" t="n">
-        <v>29.242984257358</v>
+        <v>0.280701754385965</v>
       </c>
       <c r="K17" t="n">
-        <v>1748.96102326323</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1433.44990356535</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1599.66923571951</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C18" t="n">
-        <v>0.332</v>
+        <v>0.112</v>
       </c>
       <c r="D18" t="n">
-        <v>0.332</v>
+        <v>0.27</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0166041453490894</v>
+        <v>0.0117740106697488</v>
       </c>
       <c r="F18" t="n">
-        <v>0.168</v>
+        <v>0.388</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>0.105964912280702</v>
+        <v>32.9199178644764</v>
       </c>
       <c r="J18" t="n">
-        <v>23.6440793976728</v>
+        <v>0.302222222222222</v>
       </c>
       <c r="K18" t="n">
-        <v>1488.28503086685</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1434.4081877527</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1589.15219864359</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" t="n">
-        <v>0.324923076923077</v>
+        <v>0.256923076923077</v>
       </c>
       <c r="D19" t="n">
-        <v>0.324923076923077</v>
+        <v>0.256923076923077</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0164287343379477</v>
+        <v>0.0112614481159006</v>
       </c>
       <c r="F19" t="n">
-        <v>0.175076923076923</v>
+        <v>0.243076923076923</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>0.131578947368421</v>
+        <v>23.3839835728953</v>
       </c>
       <c r="J19" t="n">
-        <v>28.6762491444216</v>
+        <v>0.200350877192982</v>
       </c>
       <c r="K19" t="n">
-        <v>1613.30577373982</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1544.05965084548</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1450.44962245897</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.322153846153846</v>
+        <v>0.264307692307692</v>
       </c>
       <c r="D20" t="n">
-        <v>0.322153846153846</v>
+        <v>0.292881355932203</v>
       </c>
       <c r="E20" t="n">
-        <v>0.015716059483184</v>
+        <v>0.0107746987414451</v>
       </c>
       <c r="F20" t="n">
-        <v>0.177846153846154</v>
+        <v>0.235692307692308</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
-        <v>0.12140350877193</v>
+        <v>28.4681724845996</v>
       </c>
       <c r="J20" t="n">
-        <v>29.5852156057495</v>
+        <v>0.303157894736842</v>
       </c>
       <c r="K20" t="n">
-        <v>1230.64497943139</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1550.25575460791</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1508.53955667597</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.208307692307692</v>
+        <v>0.217846153846154</v>
       </c>
       <c r="D21" t="n">
-        <v>0.208307692307692</v>
+        <v>0.217846153846154</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0154620299831641</v>
+        <v>0.00927018746888276</v>
       </c>
       <c r="F21" t="n">
-        <v>0.291692307692308</v>
+        <v>0.282153846153846</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.10280701754386</v>
+        <v>28.2053388090349</v>
       </c>
       <c r="J21" t="n">
-        <v>23.5893223819302</v>
+        <v>0.219298245614035</v>
       </c>
       <c r="K21" t="n">
-        <v>1625.23203644872</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1453.59156162036</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1486.65969153085</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
       <c r="C22" t="n">
-        <v>0.119384615384615</v>
+        <v>0.0184615384615385</v>
       </c>
       <c r="D22" t="n">
-        <v>0.16</v>
+        <v>0.149491525423729</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0139955690948073</v>
+        <v>0.00924072295682361</v>
       </c>
       <c r="F22" t="n">
-        <v>0.380615384615385</v>
+        <v>0.481538461538462</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.165614035087719</v>
+        <v>27.2580424366872</v>
       </c>
       <c r="J22" t="n">
-        <v>27.2142368240931</v>
+        <v>0.154736842105263</v>
       </c>
       <c r="K22" t="n">
-        <v>1553.49247004466</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1496.09960808685</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1423.47586303</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23">
@@ -1702,40 +1558,34 @@
         <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C23" t="n">
-        <v>0.327076923076923</v>
+        <v>0.103076923076923</v>
       </c>
       <c r="D23" t="n">
-        <v>0.327076923076923</v>
+        <v>0.160338983050847</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0137440779693313</v>
+        <v>0.00902437145395422</v>
       </c>
       <c r="F23" t="n">
-        <v>0.172923076923077</v>
+        <v>0.396923076923077</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>22.8281998631075</v>
       </c>
       <c r="J23" t="n">
-        <v>30.5681040383299</v>
+        <v>0.165964912280702</v>
       </c>
       <c r="K23" t="n">
-        <v>1700.13881527886</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1548.69590538699</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1580.14078674673</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -1743,204 +1593,174 @@
         <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.370153846153846</v>
+        <v>0.111384615384615</v>
       </c>
       <c r="D24" t="n">
-        <v>0.370153846153846</v>
+        <v>0.379047619047619</v>
       </c>
       <c r="E24" t="n">
-        <v>0.013321214692126</v>
+        <v>0.00890907144771785</v>
       </c>
       <c r="F24" t="n">
-        <v>0.129846153846154</v>
+        <v>0.388615384615385</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0936842105263158</v>
+        <v>28.5201916495551</v>
       </c>
       <c r="J24" t="n">
-        <v>24.72553045859</v>
+        <v>0.129473684210526</v>
       </c>
       <c r="K24" t="n">
-        <v>1315.39153301769</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1455.09425401236</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1513.75700783214</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C25" t="n">
-        <v>0.225846153846154</v>
+        <v>0.332</v>
       </c>
       <c r="D25" t="n">
-        <v>0.238095238095238</v>
+        <v>0.332</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0131945254822884</v>
+        <v>0.00874195585731393</v>
       </c>
       <c r="F25" t="n">
-        <v>0.274153846153846</v>
+        <v>0.168</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>0.167719298245614</v>
+        <v>23.6440793976728</v>
       </c>
       <c r="J25" t="n">
-        <v>29.138945927447</v>
+        <v>0.105964912280702</v>
       </c>
       <c r="K25" t="n">
-        <v>1626.9578661762</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1481.1096391574</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1520.08673618446</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>0.190461538461538</v>
+        <v>0.0806153846153846</v>
       </c>
       <c r="D26" t="n">
-        <v>0.190461538461538</v>
+        <v>0.282380952380952</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0124981829357413</v>
+        <v>0.00855353526038573</v>
       </c>
       <c r="F26" t="n">
-        <v>0.309538461538462</v>
+        <v>0.419384615384615</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0839344262295082</v>
+        <v>32.0684462696783</v>
       </c>
       <c r="J26" t="n">
-        <v>27.5920602327173</v>
+        <v>0.16</v>
       </c>
       <c r="K26" t="n">
-        <v>1382.85841537607</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1514.67244911738</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1445.05026589174</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C27" t="n">
-        <v>0.103076923076923</v>
+        <v>0.044</v>
       </c>
       <c r="D27" t="n">
-        <v>0.160338983050847</v>
+        <v>0.160727272727273</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0122479766153823</v>
+        <v>0.0083858237968466</v>
       </c>
       <c r="F27" t="n">
-        <v>0.396923076923077</v>
+        <v>0.456</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>0.165964912280702</v>
+        <v>34.1245722108145</v>
       </c>
       <c r="J27" t="n">
-        <v>22.8281998631075</v>
+        <v>0.165614035087719</v>
       </c>
       <c r="K27" t="n">
-        <v>1512.75771811409</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1418.09250811081</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1397.2343995728</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
         <v>51</v>
       </c>
-      <c r="B28" t="s">
-        <v>34</v>
-      </c>
       <c r="C28" t="n">
-        <v>0.228</v>
+        <v>0.143384615384615</v>
       </c>
       <c r="D28" t="n">
-        <v>0.228</v>
+        <v>0.143384615384615</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0105631703366651</v>
+        <v>0.00815788236614276</v>
       </c>
       <c r="F28" t="n">
-        <v>0.272</v>
+        <v>0.356615384615385</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.110877192982456</v>
+        <v>23.895961670089</v>
       </c>
       <c r="J28" t="n">
-        <v>24.5284052019165</v>
+        <v>0.139298245614035</v>
       </c>
       <c r="K28" t="n">
-        <v>1417.96308206404</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1445.3162988372</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1401.36886950135</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -1948,40 +1768,34 @@
         <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C29" t="n">
-        <v>0.245230769230769</v>
+        <v>0.458769230769231</v>
       </c>
       <c r="D29" t="n">
-        <v>0.245230769230769</v>
+        <v>0.458769230769231</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00986243010447593</v>
+        <v>0.00769705027840497</v>
       </c>
       <c r="F29" t="n">
-        <v>0.254769230769231</v>
+        <v>0.0412307692307692</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I29" t="n">
-        <v>0.111746031746032</v>
+        <v>31.958932238193</v>
       </c>
       <c r="J29" t="n">
-        <v>27.958932238193</v>
+        <v>0.272982456140351</v>
       </c>
       <c r="K29" t="n">
-        <v>1387.35175948227</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1435.3200807196</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1561.52630943399</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
@@ -1989,40 +1803,34 @@
         <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30" t="n">
-        <v>0.112</v>
+        <v>0.321538461538462</v>
       </c>
       <c r="D30" t="n">
-        <v>0.27</v>
+        <v>0.321538461538462</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00945762479220109</v>
+        <v>0.00724512222578307</v>
       </c>
       <c r="F30" t="n">
-        <v>0.388</v>
+        <v>0.178461538461538</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>0.302222222222222</v>
+        <v>27.750855578371</v>
       </c>
       <c r="J30" t="n">
-        <v>32.9199178644764</v>
+        <v>0.13859649122807</v>
       </c>
       <c r="K30" t="n">
-        <v>1463.87324822627</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1458.84057221738</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1484.83959719207</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
@@ -2030,40 +1838,34 @@
         <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>0.321538461538462</v>
+        <v>0.170461538461538</v>
       </c>
       <c r="D31" t="n">
-        <v>0.321538461538462</v>
+        <v>0.170461538461538</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00932330425225811</v>
+        <v>0.00715643247455155</v>
       </c>
       <c r="F31" t="n">
-        <v>0.178461538461538</v>
+        <v>0.329538461538462</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I31" t="n">
-        <v>0.13859649122807</v>
+        <v>24.4709103353867</v>
       </c>
       <c r="J31" t="n">
-        <v>27.750855578371</v>
+        <v>0.128070175438597</v>
       </c>
       <c r="K31" t="n">
-        <v>1257.09062409593</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1468.80824684596</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1413.47560180465</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32">
@@ -2071,81 +1873,69 @@
         <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>0.276307692307692</v>
+        <v>0.155692307692308</v>
       </c>
       <c r="D32" t="n">
-        <v>0.276307692307692</v>
+        <v>0.163728813559322</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00852171451268553</v>
+        <v>0.00704200890767304</v>
       </c>
       <c r="F32" t="n">
-        <v>0.223692307692308</v>
+        <v>0.344307692307692</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>25.388090349076</v>
       </c>
       <c r="J32" t="n">
-        <v>21.242984257358</v>
+        <v>0.169473684210526</v>
       </c>
       <c r="K32" t="n">
-        <v>1432.6155584565</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1394.7948090508</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1425.1416315827</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" t="s">
         <v>57</v>
       </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
       <c r="C33" t="n">
-        <v>0.217846153846154</v>
+        <v>0.0603076923076923</v>
       </c>
       <c r="D33" t="n">
-        <v>0.217846153846154</v>
+        <v>0.140327868852459</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00817418240999972</v>
+        <v>0.00701240815657974</v>
       </c>
       <c r="F33" t="n">
-        <v>0.282153846153846</v>
+        <v>0.439692307692308</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.219298245614035</v>
+        <v>28.2354551676934</v>
       </c>
       <c r="J33" t="n">
-        <v>28.2053388090349</v>
+        <v>0.114736842105263</v>
       </c>
       <c r="K33" t="n">
-        <v>1232.31786737431</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1391.88816692229</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1518.35942120275</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -2153,40 +1943,34 @@
         <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C34" t="n">
-        <v>0.361230769230769</v>
+        <v>0.0963076923076923</v>
       </c>
       <c r="D34" t="n">
-        <v>0.361230769230769</v>
+        <v>0.137627118644068</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00810829148490344</v>
+        <v>0.00689559479572217</v>
       </c>
       <c r="F34" t="n">
-        <v>0.138769230769231</v>
+        <v>0.403692307692308</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>0.204561403508772</v>
+        <v>27.2826830937714</v>
       </c>
       <c r="J34" t="n">
-        <v>32.0191649555099</v>
+        <v>0.142456140350877</v>
       </c>
       <c r="K34" t="n">
-        <v>1621.44565381508</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1448.18714069982</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1496.96789848146</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35">
@@ -2194,40 +1978,34 @@
         <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C35" t="n">
-        <v>0.143384615384615</v>
+        <v>0.173230769230769</v>
       </c>
       <c r="D35" t="n">
-        <v>0.143384615384615</v>
+        <v>0.187118644067797</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00707590483694574</v>
+        <v>0.00679155421321247</v>
       </c>
       <c r="F35" t="n">
-        <v>0.356615384615385</v>
+        <v>0.326769230769231</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I35" t="n">
-        <v>0.139298245614035</v>
+        <v>32.1341546885695</v>
       </c>
       <c r="J35" t="n">
-        <v>23.895961670089</v>
+        <v>0.193684210526316</v>
       </c>
       <c r="K35" t="n">
-        <v>1429.89699827518</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1345.6061901977</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1458.97823254735</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36">
@@ -2235,40 +2013,34 @@
         <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C36" t="n">
-        <v>0.170461538461538</v>
+        <v>0.0972307692307692</v>
       </c>
       <c r="D36" t="n">
-        <v>0.170461538461538</v>
+        <v>0.2095</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00688954515134266</v>
+        <v>0.00671917096400546</v>
       </c>
       <c r="F36" t="n">
-        <v>0.329538461538462</v>
+        <v>0.402769230769231</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>0.128070175438597</v>
+        <v>26.7789185489391</v>
       </c>
       <c r="J36" t="n">
-        <v>24.4709103353867</v>
+        <v>0.113333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>1332.88975458566</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1378.34616629367</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1400.28682568561</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
@@ -2276,40 +2048,34 @@
         <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.151076923076923</v>
+        <v>0.322153846153846</v>
       </c>
       <c r="D37" t="n">
-        <v>0.319661016949153</v>
+        <v>0.322153846153846</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00663931746516016</v>
+        <v>0.0067083703632409</v>
       </c>
       <c r="F37" t="n">
-        <v>0.348923076923077</v>
+        <v>0.177846153846154</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.330877192982456</v>
+        <v>29.5852156057495</v>
       </c>
       <c r="J37" t="n">
-        <v>32.5913757700205</v>
+        <v>0.12140350877193</v>
       </c>
       <c r="K37" t="n">
-        <v>1571.15388863315</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1382.92779213082</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1495.83524497121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38">
@@ -2317,40 +2083,34 @@
         <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>0.141538461538462</v>
+        <v>0.0772307692307692</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1485</v>
+        <v>0.126</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00636550293659653</v>
+        <v>0.00657598370112659</v>
       </c>
       <c r="F38" t="n">
-        <v>0.358461538461538</v>
+        <v>0.422769230769231</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>0.174705882352941</v>
+        <v>22.9295003422313</v>
       </c>
       <c r="J38" t="n">
-        <v>26.1629021218344</v>
+        <v>0.0873684210526316</v>
       </c>
       <c r="K38" t="n">
-        <v>1225.6837219819</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1382.65421457658</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1391.87090296566</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
@@ -2358,327 +2118,279 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.260307692307692</v>
+        <v>0.324923076923077</v>
       </c>
       <c r="D39" t="n">
-        <v>0.299322033898305</v>
+        <v>0.324923076923077</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00630059765323624</v>
+        <v>0.00649127852884384</v>
       </c>
       <c r="F39" t="n">
-        <v>0.239692307692308</v>
+        <v>0.175076923076923</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I39" t="n">
-        <v>0.309824561403509</v>
+        <v>28.6762491444216</v>
       </c>
       <c r="J39" t="n">
-        <v>34.031485284052</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="K39" t="n">
-        <v>1279.4212895648</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1417.83820576077</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1492.02337886906</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>0.111384615384615</v>
+        <v>0.141538461538462</v>
       </c>
       <c r="D40" t="n">
-        <v>0.379047619047619</v>
+        <v>0.1485</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00620960432357408</v>
+        <v>0.00648610353972906</v>
       </c>
       <c r="F40" t="n">
-        <v>0.388615384615385</v>
+        <v>0.358461538461538</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I40" t="n">
-        <v>0.129473684210526</v>
+        <v>26.1629021218344</v>
       </c>
       <c r="J40" t="n">
-        <v>28.5201916495551</v>
+        <v>0.174705882352941</v>
       </c>
       <c r="K40" t="n">
-        <v>1534.86862199725</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1427.38513470566</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1372.62411856363</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>0.136307692307692</v>
+        <v>0.361230769230769</v>
       </c>
       <c r="D41" t="n">
-        <v>0.152203389830508</v>
+        <v>0.361230769230769</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00591011905663496</v>
+        <v>0.00627498006957406</v>
       </c>
       <c r="F41" t="n">
-        <v>0.363692307692308</v>
+        <v>0.138769230769231</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I41" t="n">
-        <v>0.157543859649123</v>
+        <v>32.0191649555099</v>
       </c>
       <c r="J41" t="n">
-        <v>27.7837097878166</v>
+        <v>0.204561403508772</v>
       </c>
       <c r="K41" t="n">
-        <v>1250.49310922027</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1435.6030759549</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1293.83928252634</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C42" t="n">
-        <v>0.185230769230769</v>
+        <v>0.208307692307692</v>
       </c>
       <c r="D42" t="n">
-        <v>0.185230769230769</v>
+        <v>0.208307692307692</v>
       </c>
       <c r="E42" t="n">
-        <v>0.00590645667008197</v>
+        <v>0.00610921309538186</v>
       </c>
       <c r="F42" t="n">
-        <v>0.314769230769231</v>
+        <v>0.291692307692308</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>23.5893223819302</v>
       </c>
       <c r="J42" t="n">
-        <v>22.7953456536619</v>
+        <v>0.10280701754386</v>
       </c>
       <c r="K42" t="n">
-        <v>1395.8408309069</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1375.68441167262</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1397.19113826149</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>0.152</v>
+        <v>0.225846153846154</v>
       </c>
       <c r="D43" t="n">
-        <v>0.152</v>
+        <v>0.238095238095238</v>
       </c>
       <c r="E43" t="n">
-        <v>0.00587676216272052</v>
+        <v>0.00597750708770805</v>
       </c>
       <c r="F43" t="n">
-        <v>0.348</v>
+        <v>0.274153846153846</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>29.138945927447</v>
       </c>
       <c r="J43" t="n">
-        <v>24.7145790554415</v>
+        <v>0.167719298245614</v>
       </c>
       <c r="K43" t="n">
-        <v>1262.42636883388</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1420.01934609008</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1367.45225942492</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C44" t="n">
-        <v>0.155692307692308</v>
+        <v>0.136307692307692</v>
       </c>
       <c r="D44" t="n">
-        <v>0.163728813559322</v>
+        <v>0.152203389830508</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0055159799185473</v>
+        <v>0.00583358297177121</v>
       </c>
       <c r="F44" t="n">
-        <v>0.344307692307692</v>
+        <v>0.363692307692308</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.169473684210526</v>
+        <v>27.7837097878166</v>
       </c>
       <c r="J44" t="n">
-        <v>25.388090349076</v>
+        <v>0.157543859649123</v>
       </c>
       <c r="K44" t="n">
-        <v>1544.14382366596</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1311.05307312204</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1475.280550107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C45" t="n">
-        <v>0.171076923076923</v>
+        <v>0.228</v>
       </c>
       <c r="D45" t="n">
-        <v>0.171076923076923</v>
+        <v>0.228</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00516982656614473</v>
+        <v>0.00576814761230749</v>
       </c>
       <c r="F45" t="n">
-        <v>0.328923076923077</v>
+        <v>0.272</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>24.5284052019165</v>
       </c>
       <c r="J45" t="n">
-        <v>27.4250513347023</v>
+        <v>0.110877192982456</v>
       </c>
       <c r="K45" t="n">
-        <v>1301.72375343194</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1432.72524617131</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1394.62367979902</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" t="s">
         <v>71</v>
       </c>
-      <c r="B46" t="s">
-        <v>38</v>
-      </c>
       <c r="C46" t="n">
-        <v>0.117230769230769</v>
+        <v>0.110769230769231</v>
       </c>
       <c r="D46" t="n">
-        <v>0.117230769230769</v>
+        <v>0.1275</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00513977264066718</v>
+        <v>0.00565399098147203</v>
       </c>
       <c r="F46" t="n">
-        <v>0.382769230769231</v>
+        <v>0.389230769230769</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0845614035087719</v>
+        <v>27.6577686516085</v>
       </c>
       <c r="J46" t="n">
-        <v>24.4873374401095</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="K46" t="n">
-        <v>1214.16162024139</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1382.98346396969</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1320.55160751415</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47">
@@ -2686,909 +2398,777 @@
         <v>72</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="C47" t="n">
-        <v>0.124923076923077</v>
+        <v>0.370153846153846</v>
       </c>
       <c r="D47" t="n">
-        <v>0.124923076923077</v>
+        <v>0.370153846153846</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00483545904873934</v>
+        <v>0.00564498507801906</v>
       </c>
       <c r="F47" t="n">
-        <v>0.375076923076923</v>
+        <v>0.129846153846154</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>24.72553045859</v>
       </c>
       <c r="J47" t="n">
-        <v>22.8418891170431</v>
+        <v>0.0936842105263158</v>
       </c>
       <c r="K47" t="n">
-        <v>1508.73473992406</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1349.05057356984</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1378.14921120525</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="C48" t="n">
-        <v>0.115076923076923</v>
+        <v>0.115692307692308</v>
       </c>
       <c r="D48" t="n">
-        <v>0.115076923076923</v>
+        <v>0.115692307692308</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00472091842123389</v>
+        <v>0.00552212310744227</v>
       </c>
       <c r="F48" t="n">
-        <v>0.384923076923077</v>
+        <v>0.384307692307692</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>28.435318275154</v>
       </c>
       <c r="J48" t="n">
-        <v>23.0280629705681</v>
+        <v>0.096140350877193</v>
       </c>
       <c r="K48" t="n">
-        <v>1489.4012128709</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1341.25980770169</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1401.47383286135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0723076923076923</v>
+        <v>0.119384615384615</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0723076923076923</v>
+        <v>0.16</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00469289582066904</v>
+        <v>0.00520625877723686</v>
       </c>
       <c r="F49" t="n">
-        <v>0.427692307692308</v>
+        <v>0.380615384615385</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>27.2142368240931</v>
       </c>
       <c r="J49" t="n">
-        <v>22.8692676249144</v>
+        <v>0.165614035087719</v>
       </c>
       <c r="K49" t="n">
-        <v>1395.67989451059</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1378.88729757936</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1290.86945317176</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C50" t="n">
-        <v>0.139076923076923</v>
+        <v>0.0329230769230769</v>
       </c>
       <c r="D50" t="n">
-        <v>0.139076923076923</v>
+        <v>0.0742857142857143</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00463316549973235</v>
+        <v>0.005051912319567</v>
       </c>
       <c r="F50" t="n">
-        <v>0.360923076923077</v>
+        <v>0.467076923076923</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>24.5475701574264</v>
       </c>
       <c r="J50" t="n">
-        <v>23.9069130732375</v>
+        <v>0.0764912280701754</v>
       </c>
       <c r="K50" t="n">
-        <v>1500.95317698071</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1356.45929364849</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1387.62707309998</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>0.101538461538462</v>
+        <v>0.142153846153846</v>
       </c>
       <c r="D51" t="n">
-        <v>0.101538461538462</v>
+        <v>0.142153846153846</v>
       </c>
       <c r="E51" t="n">
-        <v>0.00451288405218685</v>
+        <v>0.00500875768713946</v>
       </c>
       <c r="F51" t="n">
-        <v>0.398461538461538</v>
+        <v>0.357846153846154</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>25.8699520876112</v>
       </c>
       <c r="J51" t="n">
-        <v>22.7542778918549</v>
+        <v>0.127058823529412</v>
       </c>
       <c r="K51" t="n">
-        <v>1455.93679998291</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1347.30257201768</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1355.10121362168</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0972307692307692</v>
+        <v>0.0812307692307692</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2095</v>
+        <v>0.105423728813559</v>
       </c>
       <c r="E52" t="n">
-        <v>0.00450993852943132</v>
+        <v>0.00455048763333283</v>
       </c>
       <c r="F52" t="n">
-        <v>0.402769230769231</v>
+        <v>0.418769230769231</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.113333333333333</v>
+        <v>27.4907597535934</v>
       </c>
       <c r="J52" t="n">
-        <v>26.7789185489391</v>
+        <v>0.109122807017544</v>
       </c>
       <c r="K52" t="n">
-        <v>1343.51438286255</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1385.55668527546</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1315.59993754028</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C53" t="n">
-        <v>0.072</v>
+        <v>0.104</v>
       </c>
       <c r="D53" t="n">
-        <v>0.072</v>
+        <v>0.104</v>
       </c>
       <c r="E53" t="n">
-        <v>0.00447616353317436</v>
+        <v>0.00434523886569852</v>
       </c>
       <c r="F53" t="n">
-        <v>0.428</v>
+        <v>0.396</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I53" t="n">
+        <v>20.5913757700205</v>
+      </c>
+      <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="J53" t="n">
-        <v>22.4421629021218</v>
-      </c>
       <c r="K53" t="n">
-        <v>1356.83697567042</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1345.76044819342</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1352.8010955241</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0584615384615385</v>
+        <v>0.0864615384615385</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0584615384615385</v>
+        <v>0.171904761904762</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00426067637817385</v>
+        <v>0.00411654294208475</v>
       </c>
       <c r="F54" t="n">
-        <v>0.441538461538462</v>
+        <v>0.413538461538462</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>30.9322381930185</v>
       </c>
       <c r="J54" t="n">
-        <v>22.7734428473648</v>
+        <v>0.116842105263158</v>
       </c>
       <c r="K54" t="n">
-        <v>1344.69426837203</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1342.20853986321</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1358.44226778984</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C55" t="n">
-        <v>0.110769230769231</v>
+        <v>0.0929230769230769</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1275</v>
+        <v>0.104406779661017</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00393538586625176</v>
+        <v>0.00407519190433008</v>
       </c>
       <c r="F55" t="n">
-        <v>0.389230769230769</v>
+        <v>0.407076923076923</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H55" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.131578947368421</v>
+        <v>26.6475017111567</v>
       </c>
       <c r="J55" t="n">
-        <v>27.6577686516085</v>
+        <v>0.108070175438596</v>
       </c>
       <c r="K55" t="n">
-        <v>1150.37812819264</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1350.13497245266</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1403.04482404585</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0526153846153846</v>
+        <v>0.117230769230769</v>
       </c>
       <c r="D56" t="n">
-        <v>0.122380952380952</v>
+        <v>0.117230769230769</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00365598339236754</v>
+        <v>0.00398489943611272</v>
       </c>
       <c r="F56" t="n">
-        <v>0.447384615384615</v>
+        <v>0.382769230769231</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I56" t="n">
-        <v>0.108421052631579</v>
+        <v>24.4873374401095</v>
       </c>
       <c r="J56" t="n">
-        <v>28.6789869952088</v>
+        <v>0.0845614035087719</v>
       </c>
       <c r="K56" t="n">
-        <v>1466.60561581011</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1355.27921646996</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1392.88707384781</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0929230769230769</v>
+        <v>0.0458461538461538</v>
       </c>
       <c r="D57" t="n">
-        <v>0.104406779661017</v>
+        <v>0.213898305084746</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00360612035596816</v>
+        <v>0.00390930191975027</v>
       </c>
       <c r="F57" t="n">
-        <v>0.407076923076923</v>
+        <v>0.454153846153846</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.108070175438596</v>
+        <v>35.4442162902122</v>
       </c>
       <c r="J57" t="n">
-        <v>26.6475017111567</v>
+        <v>0.0996491228070175</v>
       </c>
       <c r="K57" t="n">
-        <v>1468.74951489673</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1350.91736681457</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1306.24531691601</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C58" t="n">
-        <v>0.114769230769231</v>
+        <v>0.276307692307692</v>
       </c>
       <c r="D58" t="n">
-        <v>0.114769230769231</v>
+        <v>0.276307692307692</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00355343357833906</v>
+        <v>0.0039063560689358</v>
       </c>
       <c r="F58" t="n">
-        <v>0.385230769230769</v>
+        <v>0.223692307692308</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I58" t="n">
+        <v>21.242984257358</v>
+      </c>
+      <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="J58" t="n">
-        <v>24.1724845995893</v>
-      </c>
       <c r="K58" t="n">
-        <v>1423.52127078282</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1330.82363574782</v>
-      </c>
-      <c r="M58" t="n">
-        <v>1368.74613714031</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0772307692307692</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0.126</v>
+        <v>0.0647457627118644</v>
       </c>
       <c r="E59" t="n">
-        <v>0.00343554272775236</v>
+        <v>0.0038902247148289</v>
       </c>
       <c r="F59" t="n">
-        <v>0.422769230769231</v>
+        <v>0.5</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H59" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0873684210526316</v>
+        <v>24.9390828199863</v>
       </c>
       <c r="J59" t="n">
-        <v>22.9295003422313</v>
+        <v>0.0670175438596491</v>
       </c>
       <c r="K59" t="n">
-        <v>1241.13353387424</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1313.99836675921</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1270.97275630001</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C60" t="n">
-        <v>0.104</v>
+        <v>0.107384615384615</v>
       </c>
       <c r="D60" t="n">
-        <v>0.104</v>
+        <v>0.107384615384615</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00336782692076057</v>
+        <v>0.00364720723278634</v>
       </c>
       <c r="F60" t="n">
-        <v>0.396</v>
+        <v>0.392615384615385</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>26.9568788501027</v>
       </c>
       <c r="J60" t="n">
-        <v>20.5913757700205</v>
+        <v>0.0996491228070175</v>
       </c>
       <c r="K60" t="n">
-        <v>1340.66635892101</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1323.558085724</v>
-      </c>
-      <c r="M60" t="n">
-        <v>1210.97472684585</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0812307692307692</v>
+        <v>0.0664615384615385</v>
       </c>
       <c r="D61" t="n">
-        <v>0.105423728813559</v>
+        <v>0.0874576271186441</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00327872469860892</v>
+        <v>0.00350671985477239</v>
       </c>
       <c r="F61" t="n">
-        <v>0.418769230769231</v>
+        <v>0.433538461538462</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I61" t="n">
-        <v>0.109122807017544</v>
+        <v>26.7624914442163</v>
       </c>
       <c r="J61" t="n">
-        <v>27.4907597535934</v>
+        <v>0.0905263157894737</v>
       </c>
       <c r="K61" t="n">
-        <v>1307.03500357302</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1372.44300068653</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1257.06576200764</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C62" t="n">
-        <v>0.157846153846154</v>
+        <v>0.0636923076923077</v>
       </c>
       <c r="D62" t="n">
-        <v>0.157846153846154</v>
+        <v>0.133015873015873</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00317905153767323</v>
+        <v>0.00335890091250795</v>
       </c>
       <c r="F62" t="n">
-        <v>0.342153846153846</v>
+        <v>0.436307692307692</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>31.419575633128</v>
       </c>
       <c r="J62" t="n">
-        <v>26.7433264887064</v>
+        <v>0.0410526315789474</v>
       </c>
       <c r="K62" t="n">
-        <v>1317.99439086</v>
-      </c>
-      <c r="L62" t="n">
-        <v>1345.9016154514</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1406.13491185025</v>
+        <v>181</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C63" t="n">
-        <v>0.142153846153846</v>
+        <v>0.110769230769231</v>
       </c>
       <c r="D63" t="n">
-        <v>0.142153846153846</v>
+        <v>0.246190476190476</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00303037227302907</v>
+        <v>0.003357608762221</v>
       </c>
       <c r="F63" t="n">
-        <v>0.357846153846154</v>
+        <v>0.389230769230769</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.127058823529412</v>
+        <v>33.7577002053388</v>
       </c>
       <c r="J63" t="n">
-        <v>25.8699520876112</v>
+        <v>0.0905263157894737</v>
       </c>
       <c r="K63" t="n">
-        <v>1330.77715644626</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1274.8375564043</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1414.09617633426</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C64" t="n">
-        <v>0.107384615384615</v>
+        <v>0.0636923076923077</v>
       </c>
       <c r="D64" t="n">
-        <v>0.107384615384615</v>
+        <v>0.0885</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00296127685792299</v>
+        <v>0.00325208341747461</v>
       </c>
       <c r="F64" t="n">
-        <v>0.392615384615385</v>
+        <v>0.436307692307692</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0996491228070175</v>
+        <v>24.1587953456537</v>
       </c>
       <c r="J64" t="n">
-        <v>26.9568788501027</v>
+        <v>0.0294736842105263</v>
       </c>
       <c r="K64" t="n">
-        <v>1386.57993933099</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1330.33398602716</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1314.04968651918</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0846153846153846</v>
+        <v>0.124923076923077</v>
       </c>
       <c r="D65" t="n">
-        <v>0.198</v>
+        <v>0.246190476190476</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00293013000516573</v>
+        <v>0.00321454430249937</v>
       </c>
       <c r="F65" t="n">
-        <v>0.415384615384615</v>
+        <v>0.375076923076923</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I65" t="n">
-        <v>0.232941176470588</v>
+        <v>31.895961670089</v>
       </c>
       <c r="J65" t="n">
-        <v>33.9739904175222</v>
+        <v>0.0694736842105263</v>
       </c>
       <c r="K65" t="n">
-        <v>1225.88009026306</v>
-      </c>
-      <c r="L65" t="n">
-        <v>1377.33444148005</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1365.90879169601</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C66" t="n">
-        <v>0.124923076923077</v>
+        <v>0.110461538461538</v>
       </c>
       <c r="D66" t="n">
-        <v>0.246190476190476</v>
+        <v>0.110461538461538</v>
       </c>
       <c r="E66" t="n">
-        <v>0.00277864573718489</v>
+        <v>0.00318417113725092</v>
       </c>
       <c r="F66" t="n">
-        <v>0.375076923076923</v>
+        <v>0.389538461538462</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0694736842105263</v>
+        <v>27.958932238193</v>
       </c>
       <c r="J66" t="n">
-        <v>31.895961670089</v>
+        <v>0.0698245614035088</v>
       </c>
       <c r="K66" t="n">
-        <v>1080.37269595228</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1392.8901065853</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1396.73705554117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0547692307692308</v>
+        <v>0.0526153846153846</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0547692307692308</v>
+        <v>0.122380952380952</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0025674173139128</v>
+        <v>0.00316807991746341</v>
       </c>
       <c r="F67" t="n">
-        <v>0.445230769230769</v>
+        <v>0.447384615384615</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H67" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>28.6789869952088</v>
       </c>
       <c r="J67" t="n">
-        <v>22.3819301848049</v>
+        <v>0.108421052631579</v>
       </c>
       <c r="K67" t="n">
-        <v>1308.64619952678</v>
-      </c>
-      <c r="L67" t="n">
-        <v>1263.54407969337</v>
-      </c>
-      <c r="M67" t="n">
-        <v>1356.42724816645</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0233846153846154</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0233846153846154</v>
+        <v>0.039047619047619</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00255755438394979</v>
+        <v>0.00314556711080639</v>
       </c>
       <c r="F68" t="n">
-        <v>0.476615384615385</v>
+        <v>0.5</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H68" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>25.596167008898</v>
       </c>
       <c r="J68" t="n">
-        <v>23.3593429158111</v>
+        <v>0.0455555555555556</v>
       </c>
       <c r="K68" t="n">
-        <v>1249.63962474064</v>
-      </c>
-      <c r="L68" t="n">
-        <v>1311.81436104358</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1263.8132653586</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C69" t="n">
         <v>0.0443076923076923</v>
@@ -3597,646 +3177,550 @@
         <v>0.0443076923076923</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0025062998085711</v>
+        <v>0.00314218814524435</v>
       </c>
       <c r="F69" t="n">
         <v>0.455692307692308</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I69" t="n">
+        <v>21.305954825462</v>
+      </c>
+      <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="n">
-        <v>21.305954825462</v>
-      </c>
       <c r="K69" t="n">
-        <v>1267.12180093125</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1273.44276960971</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1271.72580558593</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0972307692307692</v>
+        <v>0.185230769230769</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0972307692307692</v>
+        <v>0.185230769230769</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0024453038637718</v>
+        <v>0.0031107257610494</v>
       </c>
       <c r="F70" t="n">
-        <v>0.402769230769231</v>
+        <v>0.314769230769231</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H70" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I70" t="n">
+        <v>22.7953456536619</v>
+      </c>
+      <c r="J70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="n">
-        <v>27.378507871321</v>
-      </c>
       <c r="K70" t="n">
-        <v>1473.99512474978</v>
-      </c>
-      <c r="L70" t="n">
-        <v>1283.98948951066</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1486.7630382211</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C71" t="n">
-        <v>0.173230769230769</v>
+        <v>0.0236923076923077</v>
       </c>
       <c r="D71" t="n">
-        <v>0.187118644067797</v>
+        <v>0.0236923076923077</v>
       </c>
       <c r="E71" t="n">
-        <v>0.00239622360781159</v>
+        <v>0.00309973238606606</v>
       </c>
       <c r="F71" t="n">
-        <v>0.326769230769231</v>
+        <v>0.476307692307692</v>
       </c>
       <c r="G71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H71" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I71" t="n">
-        <v>0.193684210526316</v>
+        <v>21.5989048596851</v>
       </c>
       <c r="J71" t="n">
-        <v>32.1341546885695</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1100.18110230003</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1316.10375150417</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1431.66528916872</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0664615384615385</v>
+        <v>0.0421538461538462</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0874576271186441</v>
+        <v>0.07</v>
       </c>
       <c r="E72" t="n">
-        <v>0.00235126635116107</v>
+        <v>0.003068466487704</v>
       </c>
       <c r="F72" t="n">
-        <v>0.433538461538462</v>
+        <v>0.457846153846154</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0905263157894737</v>
+        <v>28.6461327857632</v>
       </c>
       <c r="J72" t="n">
-        <v>26.7624914442163</v>
+        <v>0.0487719298245614</v>
       </c>
       <c r="K72" t="n">
-        <v>1400.30339675546</v>
-      </c>
-      <c r="L72" t="n">
-        <v>1306.64911929176</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1283.23286690874</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C73" t="n">
-        <v>0.115692307692308</v>
+        <v>0.101538461538462</v>
       </c>
       <c r="D73" t="n">
-        <v>0.115692307692308</v>
+        <v>0.101538461538462</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00234470953271127</v>
+        <v>0.00296566574672139</v>
       </c>
       <c r="F73" t="n">
-        <v>0.384307692307692</v>
+        <v>0.398461538461538</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.096140350877193</v>
+        <v>22.7542778918549</v>
       </c>
       <c r="J73" t="n">
-        <v>28.435318275154</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1197.74688931425</v>
-      </c>
-      <c r="L73" t="n">
-        <v>1332.14989303076</v>
-      </c>
-      <c r="M73" t="n">
-        <v>1300.34641790998</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C74" t="n">
-        <v>0.110461538461538</v>
+        <v>0.00738461538461538</v>
       </c>
       <c r="D74" t="n">
-        <v>0.110461538461538</v>
+        <v>0.0075</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0022437307168211</v>
+        <v>0.00289879599789861</v>
       </c>
       <c r="F74" t="n">
-        <v>0.389538461538462</v>
+        <v>0.492615384615385</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" t="n">
+        <v>22.1930184804928</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
         <v>16</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.0698245614035088</v>
-      </c>
-      <c r="J74" t="n">
-        <v>27.958932238193</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1126.41736147765</v>
-      </c>
-      <c r="L74" t="n">
-        <v>1317.69814422186</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1338.81290970126</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0636923076923077</v>
+        <v>0.0584615384615385</v>
       </c>
       <c r="D75" t="n">
-        <v>0.133015873015873</v>
+        <v>0.0584615384615385</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0021929196017823</v>
+        <v>0.00284517930059882</v>
       </c>
       <c r="F75" t="n">
-        <v>0.436307692307692</v>
+        <v>0.441538461538462</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H75" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0410526315789474</v>
+        <v>22.7734428473648</v>
       </c>
       <c r="J75" t="n">
-        <v>31.419575633128</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1213.37213104866</v>
-      </c>
-      <c r="L75" t="n">
-        <v>1395.03171287989</v>
-      </c>
-      <c r="M75" t="n">
-        <v>1281.80709561178</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0963076923076923</v>
+        <v>0.124923076923077</v>
       </c>
       <c r="D76" t="n">
-        <v>0.137627118644068</v>
+        <v>0.124923076923077</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00203634433909804</v>
+        <v>0.00279413702383724</v>
       </c>
       <c r="F76" t="n">
-        <v>0.403692307692308</v>
+        <v>0.375076923076923</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H76" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I76" t="n">
-        <v>0.142456140350877</v>
+        <v>22.8418891170431</v>
       </c>
       <c r="J76" t="n">
-        <v>27.2826830937714</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1407.86261770998</v>
-      </c>
-      <c r="L76" t="n">
-        <v>1228.00658738988</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1419.24521602762</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C77" t="n">
-        <v>0.110769230769231</v>
+        <v>0.245230769230769</v>
       </c>
       <c r="D77" t="n">
-        <v>0.246190476190476</v>
+        <v>0.245230769230769</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00194618280039287</v>
+        <v>0.00277993426363863</v>
       </c>
       <c r="F77" t="n">
-        <v>0.389230769230769</v>
+        <v>0.254769230769231</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.0905263157894737</v>
+        <v>27.958932238193</v>
       </c>
       <c r="J77" t="n">
-        <v>33.7577002053388</v>
+        <v>0.111746031746032</v>
       </c>
       <c r="K77" t="n">
-        <v>1134.15683374376</v>
-      </c>
-      <c r="L77" t="n">
-        <v>1381.51269887943</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1332.28119598812</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0529230769230769</v>
+        <v>0.190461538461538</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0529230769230769</v>
+        <v>0.190461538461538</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00191197551844747</v>
+        <v>0.00273888461727146</v>
       </c>
       <c r="F78" t="n">
-        <v>0.447076923076923</v>
+        <v>0.309538461538462</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H78" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>27.5920602327173</v>
       </c>
       <c r="J78" t="n">
-        <v>24.6461327857632</v>
+        <v>0.0839344262295082</v>
       </c>
       <c r="K78" t="n">
-        <v>1333.71992290971</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1285.67345625525</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1264.52953059235</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0458461538461538</v>
+        <v>0.072</v>
       </c>
       <c r="D79" t="n">
-        <v>0.213898305084746</v>
+        <v>0.072</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00188755267100265</v>
+        <v>0.00272737024066106</v>
       </c>
       <c r="F79" t="n">
-        <v>0.454153846153846</v>
+        <v>0.428</v>
       </c>
       <c r="G79" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H79" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0996491228070175</v>
+        <v>22.4421629021218</v>
       </c>
       <c r="J79" t="n">
-        <v>35.4442162902122</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1217.17083414454</v>
-      </c>
-      <c r="L79" t="n">
-        <v>1435.18975329966</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1218.85908755817</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0636923076923077</v>
+        <v>0.0547692307692308</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0885</v>
+        <v>0.0547692307692308</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0017819515437585</v>
+        <v>0.00271027815747836</v>
       </c>
       <c r="F80" t="n">
-        <v>0.436307692307692</v>
+        <v>0.445230769230769</v>
       </c>
       <c r="G80" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H80" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0294736842105263</v>
+        <v>22.3819301848049</v>
       </c>
       <c r="J80" t="n">
-        <v>24.1587953456537</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1296.85815093371</v>
-      </c>
-      <c r="L80" t="n">
-        <v>1266.9068834077</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1238.67713438405</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B81" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0329230769230769</v>
+        <v>0.0206153846153846</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0742857142857143</v>
+        <v>0.0933333333333333</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00171806189625177</v>
+        <v>0.00267113058058618</v>
       </c>
       <c r="F81" t="n">
-        <v>0.467076923076923</v>
+        <v>0.479384615384615</v>
       </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H81" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0764912280701754</v>
+        <v>31.5373032169747</v>
       </c>
       <c r="J81" t="n">
-        <v>24.5475701574264</v>
+        <v>0.0947368421052632</v>
       </c>
       <c r="K81" t="n">
-        <v>1313.79526817923</v>
-      </c>
-      <c r="L81" t="n">
-        <v>1239.587809522</v>
-      </c>
-      <c r="M81" t="n">
-        <v>1267.96111111346</v>
+        <v>107</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0535384615384615</v>
+        <v>0.0664615384615385</v>
       </c>
       <c r="D82" t="n">
-        <v>0.158095238095238</v>
+        <v>0.0664615384615385</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00168929710725165</v>
+        <v>0.00267028797248846</v>
       </c>
       <c r="F82" t="n">
-        <v>0.446461538461538</v>
+        <v>0.433538461538462</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H82" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0652631578947368</v>
+        <v>30.6009582477755</v>
       </c>
       <c r="J82" t="n">
-        <v>30.6255989048597</v>
+        <v>0.0596491228070175</v>
       </c>
       <c r="K82" t="n">
-        <v>1460.36725347938</v>
-      </c>
-      <c r="L82" t="n">
-        <v>1280.18391446566</v>
-      </c>
-      <c r="M82" t="n">
-        <v>1416.91561649289</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0236923076923077</v>
+        <v>0.0723076923076923</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0236923076923077</v>
+        <v>0.0723076923076923</v>
       </c>
       <c r="E83" t="n">
-        <v>0.00168285229043493</v>
+        <v>0.00265668424378664</v>
       </c>
       <c r="F83" t="n">
-        <v>0.476307692307692</v>
+        <v>0.427692307692308</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H83" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I83" t="n">
+        <v>22.8692676249144</v>
+      </c>
+      <c r="J83" t="n">
         <v>0</v>
       </c>
-      <c r="J83" t="n">
-        <v>21.5989048596851</v>
-      </c>
       <c r="K83" t="n">
-        <v>1272.48973248935</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1231.95428559327</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1234.10685122193</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0603076923076923</v>
+        <v>0.115076923076923</v>
       </c>
       <c r="D84" t="n">
-        <v>0.140327868852459</v>
+        <v>0.115076923076923</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00165615521821593</v>
+        <v>0.00259340634318743</v>
       </c>
       <c r="F84" t="n">
-        <v>0.439692307692308</v>
+        <v>0.384923076923077</v>
       </c>
       <c r="G84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H84" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I84" t="n">
-        <v>0.114736842105263</v>
+        <v>23.0280629705681</v>
       </c>
       <c r="J84" t="n">
-        <v>28.2354551676934</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1338.86056255086</v>
-      </c>
-      <c r="L84" t="n">
-        <v>1275.20037989351</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1272.09619533949</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
@@ -4244,40 +3728,34 @@
         <v>114</v>
       </c>
       <c r="B85" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0806153846153846</v>
+        <v>0.114769230769231</v>
       </c>
       <c r="D85" t="n">
-        <v>0.282380952380952</v>
+        <v>0.114769230769231</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00162288884188412</v>
+        <v>0.00252396655542051</v>
       </c>
       <c r="F85" t="n">
-        <v>0.419384615384615</v>
+        <v>0.385230769230769</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H85" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I85" t="n">
-        <v>0.16</v>
+        <v>24.1724845995893</v>
       </c>
       <c r="J85" t="n">
-        <v>32.0684462696783</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1372.78552350997</v>
-      </c>
-      <c r="L85" t="n">
-        <v>1271.65580119664</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1397.05935600254</v>
+        <v>37</v>
       </c>
     </row>
     <row r="86">
@@ -4285,40 +3763,34 @@
         <v>115</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0864615384615385</v>
+        <v>0.0233846153846154</v>
       </c>
       <c r="D86" t="n">
-        <v>0.171904761904762</v>
+        <v>0.0233846153846154</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00158032013615363</v>
+        <v>0.00248529826040687</v>
       </c>
       <c r="F86" t="n">
-        <v>0.413538461538462</v>
+        <v>0.476615384615385</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H86" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I86" t="n">
-        <v>0.116842105263158</v>
+        <v>23.3593429158111</v>
       </c>
       <c r="J86" t="n">
-        <v>30.9322381930185</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>1407.92052788336</v>
-      </c>
-      <c r="L86" t="n">
-        <v>1271.84990718483</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1375.97129032249</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87">
@@ -4326,204 +3798,174 @@
         <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0184615384615385</v>
+        <v>0.0446153846153846</v>
       </c>
       <c r="D87" t="n">
-        <v>0.149491525423729</v>
+        <v>0.0715254237288136</v>
       </c>
       <c r="E87" t="n">
-        <v>0.00135039560995335</v>
+        <v>0.00247550657432368</v>
       </c>
       <c r="F87" t="n">
-        <v>0.481538461538462</v>
+        <v>0.455384615384615</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H87" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I87" t="n">
-        <v>0.154736842105263</v>
+        <v>30.4640657084189</v>
       </c>
       <c r="J87" t="n">
-        <v>27.2580424366872</v>
+        <v>0.0740350877192982</v>
       </c>
       <c r="K87" t="n">
-        <v>1264.16285123337</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1220.31669063585</v>
-      </c>
-      <c r="M87" t="n">
-        <v>1264.98807928171</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B88" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0664615384615385</v>
+        <v>0.139076923076923</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0664615384615385</v>
+        <v>0.139076923076923</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00114683274362563</v>
+        <v>0.00235871715502602</v>
       </c>
       <c r="F88" t="n">
-        <v>0.433538461538462</v>
+        <v>0.360923076923077</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0596491228070175</v>
+        <v>23.9069130732375</v>
       </c>
       <c r="J88" t="n">
-        <v>30.6009582477755</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1246.21586376132</v>
-      </c>
-      <c r="L88" t="n">
-        <v>1293.93989170002</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1237.05565348768</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0190769230769231</v>
+        <v>0.152</v>
       </c>
       <c r="D89" t="n">
-        <v>0.112881355932203</v>
+        <v>0.152</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00112095234645846</v>
+        <v>0.00228892899189821</v>
       </c>
       <c r="F89" t="n">
-        <v>0.480923076923077</v>
+        <v>0.348</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H89" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I89" t="n">
-        <v>0.116842105263158</v>
+        <v>24.7145790554415</v>
       </c>
       <c r="J89" t="n">
-        <v>33.4592744695414</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>1219.65816771157</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1271.77447289612</v>
-      </c>
-      <c r="M89" t="n">
-        <v>1364.66803830286</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B90" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C90" t="n">
-        <v>0.00707692307692308</v>
+        <v>0.0535384615384615</v>
       </c>
       <c r="D90" t="n">
-        <v>0.00707692307692308</v>
+        <v>0.158095238095238</v>
       </c>
       <c r="E90" t="n">
-        <v>0.000994856428212806</v>
+        <v>0.00222550688274606</v>
       </c>
       <c r="F90" t="n">
-        <v>0.492923076923077</v>
+        <v>0.446461538461538</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H90" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>30.6255989048597</v>
       </c>
       <c r="J90" t="n">
-        <v>25.5277207392197</v>
+        <v>0.0652631578947368</v>
       </c>
       <c r="K90" t="n">
-        <v>1289.48481198342</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1206.02256186022</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1261.74644757135</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>120</v>
+      </c>
+      <c r="B91" t="s">
         <v>121</v>
       </c>
-      <c r="B91" t="s">
-        <v>113</v>
-      </c>
       <c r="C91" t="n">
-        <v>0.00738461538461538</v>
+        <v>0.0270769230769231</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0075</v>
+        <v>0.0374603174603175</v>
       </c>
       <c r="E91" t="n">
-        <v>0.000991702705912185</v>
+        <v>0.00215683741456084</v>
       </c>
       <c r="F91" t="n">
-        <v>0.492615384615385</v>
+        <v>0.472923076923077</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H91" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I91" t="n">
+        <v>27.5455167693361</v>
+      </c>
+      <c r="J91" t="n">
         <v>0</v>
       </c>
-      <c r="J91" t="n">
-        <v>22.1930184804928</v>
-      </c>
       <c r="K91" t="n">
-        <v>1184.66665875218</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1196.46640220873</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1146.53835368705</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92">
@@ -4531,40 +3973,34 @@
         <v>122</v>
       </c>
       <c r="B92" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="C92" t="n">
-        <v>0.00676923076923077</v>
+        <v>0.0135384615384615</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00676923076923077</v>
+        <v>0.0135384615384615</v>
       </c>
       <c r="E92" t="n">
-        <v>0.000986770645209324</v>
+        <v>0.00213858379488743</v>
       </c>
       <c r="F92" t="n">
-        <v>0.493230769230769</v>
+        <v>0.486461538461538</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H92" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I92" t="n">
+        <v>24.0438056125941</v>
+      </c>
+      <c r="J92" t="n">
         <v>0</v>
       </c>
-      <c r="J92" t="n">
-        <v>24.580424366872</v>
-      </c>
       <c r="K92" t="n">
-        <v>1253.85034268986</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1203.19290498576</v>
-      </c>
-      <c r="M92" t="n">
-        <v>1226.86348909833</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -4572,40 +4008,34 @@
         <v>123</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>0.0190769230769231</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0647457627118644</v>
+        <v>0.112881355932203</v>
       </c>
       <c r="E93" t="n">
-        <v>0.000931714196081385</v>
+        <v>0.00204476927063378</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5</v>
+        <v>0.480923076923077</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H93" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0670175438596491</v>
+        <v>33.4592744695414</v>
       </c>
       <c r="J93" t="n">
-        <v>24.9390828199863</v>
+        <v>0.116842105263158</v>
       </c>
       <c r="K93" t="n">
-        <v>1279.78803514376</v>
-      </c>
-      <c r="L93" t="n">
-        <v>1177.82312327424</v>
-      </c>
-      <c r="M93" t="n">
-        <v>1216.97688731791</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94">
@@ -4613,130 +4043,112 @@
         <v>124</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.0529230769230769</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.0529230769230769</v>
       </c>
       <c r="E94" t="n">
-        <v>0.000908419379773931</v>
+        <v>0.0019819731785575</v>
       </c>
       <c r="F94" t="n">
-        <v>0.486461538461538</v>
+        <v>0.447076923076923</v>
       </c>
       <c r="G94" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" t="n">
+        <v>24.6461327857632</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>15</v>
-      </c>
-      <c r="H94" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>24.0438056125941</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1211.44098510954</v>
-      </c>
-      <c r="L94" t="n">
-        <v>1191.30147133873</v>
-      </c>
-      <c r="M94" t="n">
-        <v>1206.0825484611</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0206153846153846</v>
+        <v>0.00676923076923077</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0933333333333333</v>
+        <v>0.00676923076923077</v>
       </c>
       <c r="E95" t="n">
-        <v>0.000884388120929784</v>
+        <v>0.00197118214246645</v>
       </c>
       <c r="F95" t="n">
-        <v>0.479384615384615</v>
+        <v>0.493230769230769</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H95" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0947368421052632</v>
+        <v>24.580424366872</v>
       </c>
       <c r="J95" t="n">
-        <v>31.5373032169747</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1335.09614869109</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1224.1198382179</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1325.25478480542</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B96" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0446153846153846</v>
+        <v>0.157846153846154</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0715254237288136</v>
+        <v>0.157846153846154</v>
       </c>
       <c r="E96" t="n">
-        <v>0.000748222683901514</v>
+        <v>0.00194763081972041</v>
       </c>
       <c r="F96" t="n">
-        <v>0.455384615384615</v>
+        <v>0.342153846153846</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H96" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0740350877192982</v>
+        <v>26.7433264887064</v>
       </c>
       <c r="J96" t="n">
-        <v>30.4640657084189</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1188.27448494651</v>
-      </c>
-      <c r="L96" t="n">
-        <v>1220.41256111428</v>
-      </c>
-      <c r="M96" t="n">
-        <v>1253.29808146112</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -4745,482 +4157,410 @@
         <v>0.0176271186440678</v>
       </c>
       <c r="E97" t="n">
-        <v>0.00072095351414243</v>
+        <v>0.00179185955266578</v>
       </c>
       <c r="F97" t="n">
         <v>0.5</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H97" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" t="n">
+        <v>25.3607118412047</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
         <v>16</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>25.3607118412047</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1248.46162065852</v>
-      </c>
-      <c r="L97" t="n">
-        <v>1184.68668384022</v>
-      </c>
-      <c r="M97" t="n">
-        <v>1181.89115983615</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0421538461538462</v>
+        <v>0.00707692307692308</v>
       </c>
       <c r="D98" t="n">
-        <v>0.07</v>
+        <v>0.00707692307692308</v>
       </c>
       <c r="E98" t="n">
-        <v>0.000695155164186774</v>
+        <v>0.00169382372712174</v>
       </c>
       <c r="F98" t="n">
-        <v>0.457846153846154</v>
+        <v>0.492923076923077</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H98" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0487719298245614</v>
+        <v>25.5277207392197</v>
       </c>
       <c r="J98" t="n">
-        <v>28.6461327857632</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1294.88569704496</v>
-      </c>
-      <c r="L98" t="n">
-        <v>1199.55771996603</v>
-      </c>
-      <c r="M98" t="n">
-        <v>1214.93236428129</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B99" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.0289230769230769</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0135384615384615</v>
+        <v>0.0289230769230769</v>
       </c>
       <c r="E99" t="n">
-        <v>0.000619888131149434</v>
+        <v>0.00165364655745161</v>
       </c>
       <c r="F99" t="n">
-        <v>0.486461538461538</v>
+        <v>0.471076923076923</v>
       </c>
       <c r="G99" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H99" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>28.2737850787132</v>
       </c>
       <c r="J99" t="n">
-        <v>27.170431211499</v>
+        <v>0.0114285714285714</v>
       </c>
       <c r="K99" t="n">
-        <v>1185.72298502975</v>
-      </c>
-      <c r="L99" t="n">
-        <v>1180.74280819761</v>
-      </c>
-      <c r="M99" t="n">
-        <v>1218.48717749614</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0289230769230769</v>
+        <v>0.0972307692307692</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0289230769230769</v>
+        <v>0.0972307692307692</v>
       </c>
       <c r="E100" t="n">
-        <v>0.000606085342392592</v>
+        <v>0.00163703412385446</v>
       </c>
       <c r="F100" t="n">
-        <v>0.471076923076923</v>
+        <v>0.402769230769231</v>
       </c>
       <c r="G100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H100" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0114285714285714</v>
+        <v>27.378507871321</v>
       </c>
       <c r="J100" t="n">
-        <v>28.2737850787132</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1233.51169403177</v>
-      </c>
-      <c r="L100" t="n">
-        <v>1214.35534681034</v>
-      </c>
-      <c r="M100" t="n">
-        <v>1142.38883668489</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B101" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C101" t="n">
-        <v>0.044</v>
+        <v>0.0206153846153846</v>
       </c>
       <c r="D101" t="n">
-        <v>0.160727272727273</v>
+        <v>0.024</v>
       </c>
       <c r="E101" t="n">
-        <v>0.000534221939455651</v>
+        <v>0.00157801500745511</v>
       </c>
       <c r="F101" t="n">
-        <v>0.456</v>
+        <v>0.479384615384615</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H101" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I101" t="n">
-        <v>0.165614035087719</v>
+        <v>27.4168377823409</v>
       </c>
       <c r="J101" t="n">
-        <v>34.1245722108145</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>1349.0390402962</v>
-      </c>
-      <c r="L101" t="n">
-        <v>1181.81251826923</v>
-      </c>
-      <c r="M101" t="n">
-        <v>1271.44799007319</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B102" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D102" t="n">
-        <v>0.039047619047619</v>
+        <v>0.0263492063492063</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000409939337538844</v>
+        <v>0.00153194263761401</v>
       </c>
       <c r="F102" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H102" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I102" t="n">
-        <v>0.0455555555555556</v>
+        <v>28.4626967830253</v>
       </c>
       <c r="J102" t="n">
-        <v>25.596167008898</v>
+        <v>0.00315789473684211</v>
       </c>
       <c r="K102" t="n">
-        <v>1121.60891494279</v>
-      </c>
-      <c r="L102" t="n">
-        <v>1134.27003101503</v>
-      </c>
-      <c r="M102" t="n">
-        <v>1060.92117843046</v>
+        <v>54</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0212307692307692</v>
+        <v>0.0135384615384615</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0526984126984127</v>
+        <v>0.0135384615384615</v>
       </c>
       <c r="E103" t="n">
-        <v>0.000389867445389614</v>
+        <v>0.0015282148564229</v>
       </c>
       <c r="F103" t="n">
-        <v>0.478769230769231</v>
+        <v>0.486461538461538</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H103" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0171929824561404</v>
+        <v>27.170431211499</v>
       </c>
       <c r="J103" t="n">
-        <v>33.2950034223135</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>1116.9131099004</v>
-      </c>
-      <c r="L103" t="n">
-        <v>1200.46486140405</v>
-      </c>
-      <c r="M103" t="n">
-        <v>1230.29340322432</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B104" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C104" t="n">
-        <v>0.02</v>
+        <v>0.0212307692307692</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0263492063492063</v>
+        <v>0.0526984126984127</v>
       </c>
       <c r="E104" t="n">
-        <v>0.000383672183533412</v>
+        <v>0.00150969669601121</v>
       </c>
       <c r="F104" t="n">
-        <v>0.48</v>
+        <v>0.478769230769231</v>
       </c>
       <c r="G104" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H104" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.00315789473684211</v>
+        <v>33.2950034223135</v>
       </c>
       <c r="J104" t="n">
-        <v>28.4626967830253</v>
+        <v>0.0171929824561404</v>
       </c>
       <c r="K104" t="n">
-        <v>1180.05925954922</v>
-      </c>
-      <c r="L104" t="n">
-        <v>1146.19712818139</v>
-      </c>
-      <c r="M104" t="n">
-        <v>1169.14919463349</v>
+        <v>135</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B105" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C105" t="n">
-        <v>0.000307692307692308</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.000307692307692308</v>
+        <v>0.0548275862068966</v>
       </c>
       <c r="E105" t="n">
-        <v>0.000353550935085419</v>
+        <v>0.00141240783368951</v>
       </c>
       <c r="F105" t="n">
-        <v>0.499692307692308</v>
+        <v>0.5</v>
       </c>
       <c r="G105" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H105" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>30.4640657084189</v>
       </c>
       <c r="J105" t="n">
-        <v>29.2402464065708</v>
+        <v>0.0548275862068966</v>
       </c>
       <c r="K105" t="n">
-        <v>1174.96086217118</v>
-      </c>
-      <c r="L105" t="n">
-        <v>1160.93598102148</v>
-      </c>
-      <c r="M105" t="n">
-        <v>1130.02338324035</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B106" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0270769230769231</v>
+        <v>0.171076923076923</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0374603174603175</v>
+        <v>0.171076923076923</v>
       </c>
       <c r="E106" t="n">
-        <v>0.000353038962396952</v>
+        <v>0.00129926748500719</v>
       </c>
       <c r="F106" t="n">
-        <v>0.472923076923077</v>
+        <v>0.328923076923077</v>
       </c>
       <c r="G106" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" t="s">
+        <v>14</v>
+      </c>
+      <c r="I106" t="n">
+        <v>27.4250513347023</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
         <v>15</v>
-      </c>
-      <c r="H106" t="s">
-        <v>16</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>27.5455167693361</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1197.23394618571</v>
-      </c>
-      <c r="L106" t="n">
-        <v>1128.86958616484</v>
-      </c>
-      <c r="M106" t="n">
-        <v>1143.48493964278</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C107" t="n">
+        <v>0.327076923076923</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.327076923076923</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.00128090779349016</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.172923076923077</v>
+      </c>
+      <c r="G107" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" t="n">
+        <v>30.5681040383299</v>
+      </c>
+      <c r="J107" t="n">
         <v>0</v>
       </c>
-      <c r="D107" t="n">
-        <v>0.0548275862068966</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0.000284827584210144</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G107" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" t="s">
-        <v>16</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0.0548275862068966</v>
-      </c>
-      <c r="J107" t="n">
-        <v>30.4640657084189</v>
-      </c>
       <c r="K107" t="n">
-        <v>1212.81525680735</v>
-      </c>
-      <c r="L107" t="n">
-        <v>1114.80622485442</v>
-      </c>
-      <c r="M107" t="n">
-        <v>1164.57499958421</v>
+        <v>75</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0206153846153846</v>
+        <v>0.000307692307692308</v>
       </c>
       <c r="D108" t="n">
-        <v>0.024</v>
+        <v>0.000307692307692308</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000233982990285736</v>
+        <v>0.0010817279603888</v>
       </c>
       <c r="F108" t="n">
-        <v>0.479384615384615</v>
+        <v>0.499692307692308</v>
       </c>
       <c r="G108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H108" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I108" t="n">
+        <v>29.2402464065708</v>
+      </c>
+      <c r="J108" t="n">
         <v>0</v>
       </c>
-      <c r="J108" t="n">
-        <v>27.4168377823409</v>
-      </c>
       <c r="K108" t="n">
-        <v>1128.51836182568</v>
-      </c>
-      <c r="L108" t="n">
-        <v>1087.41393336823</v>
-      </c>
-      <c r="M108" t="n">
-        <v>1089.28138488946</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -5239,39 +4579,27 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
+        <v>27.1556161123798</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.117778644977419</v>
       </c>
-      <c r="C2" t="n">
-        <v>27.1556161123798</v>
-      </c>
       <c r="D2" t="n">
-        <v>1355.12332026162</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1356.21776199965</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1369.4997256828</v>
+        <v>83.7476635514019</v>
       </c>
     </row>
   </sheetData>
@@ -5287,18 +4615,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B2" t="n">
-        <v>0.918100182149363</v>
+        <v>0.916663023679417</v>
       </c>
     </row>
   </sheetData>
